--- a/docs/weekly/2026-06-3주차/C-lab_PoC_WBS_v5.xlsx
+++ b/docs/weekly/2026-06-3주차/C-lab_PoC_WBS_v5.xlsx
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:Y96"/>
+  <dimension ref="A2:Y99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -703,7 +703,7 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>v5 (2026-06-17 갱신: 06-3주차 점검, 완료 6건 추가)</t>
+          <t>v5 (2026-06-17 갱신: 06-3주차 점검 — 완료 6건 + 누락 3항목 추가)</t>
         </is>
       </c>
       <c r="D5" s="24" t="n"/>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="B42" s="30" t="n"/>
-      <c r="C42" s="35" t="n"/>
+      <c r="C42" s="30" t="n"/>
       <c r="D42" s="13" t="inlineStr">
         <is>
           <t>통행량 분석: ROI/Line Crossing 기반 In/Out Counting, 방향별 통행량 집계, 시간대별 유동인구 통계 생성</t>
@@ -2577,33 +2577,25 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>4.1.6</t>
         </is>
       </c>
       <c r="B43" s="30" t="n"/>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>사람 특성지표 산출 및 대시보드 연동</t>
-        </is>
-      </c>
+      <c r="C43" s="35" t="n"/>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>속도 지표 산출: Pixel-to-Meter 변환 계수 또는 Homography 기반 실제 이동속도 추정, 구간별 평균/최대/최소 속도 계산</t>
+          <t>방향성 정렬도: 객체 이동 벡터와 권장 피난방향 벡터 간 코사인 유사도 산출, 구역 평균 정렬도 도출</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>속도 지표 산출 모듈</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
+          <t>정렬도 지표(객체별 cos, 구역 avg_align)</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H43" s="37" t="inlineStr">
@@ -2617,11 +2609,7 @@
       <c r="L43" s="9" t="n"/>
       <c r="M43" s="9" t="n"/>
       <c r="N43" s="9" t="n"/>
-      <c r="O43" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="O43" s="9" t="n"/>
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
@@ -2636,19 +2624,23 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>4.2.2</t>
+          <t>4.2.1</t>
         </is>
       </c>
       <c r="B44" s="30" t="n"/>
-      <c r="C44" s="30" t="n"/>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>사람 특성지표 산출 및 대시보드 연동</t>
+        </is>
+      </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>체류 지표 산출: ROI 진입·이탈 시점 기반 Dwell Time 계산, 장기 체류 구간 분류, 시간대별 체류 분포 집계</t>
+          <t>속도 지표 산출: Pixel-to-Meter 변환 계수 또는 Homography 기반 실제 이동속도 추정, 구간별 평균/최대/최소 속도 계산</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>체류 지표 산출 모듈</t>
+          <t>속도 지표 산출 모듈</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
@@ -2691,19 +2683,19 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>4.2.3</t>
+          <t>4.2.2</t>
         </is>
       </c>
       <c r="B45" s="30" t="n"/>
       <c r="C45" s="30" t="n"/>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>혼잡도 지표 산출: ROI별 순간 인원수, 평균 밀집도, Peak Occupancy, 혼잡도 Level 산정 기준 적용</t>
+          <t>체류 지표 산출: ROI 진입·이탈 시점 기반 Dwell Time 계산, 장기 체류 구간 분류, 시간대별 체류 분포 집계</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>혼잡도 지표 산출 모듈</t>
+          <t>체류 지표 산출 모듈</t>
         </is>
       </c>
       <c r="F45" s="15" t="inlineStr">
@@ -2711,10 +2703,14 @@
           <t>2d</t>
         </is>
       </c>
-      <c r="G45" s="15" t="n"/>
-      <c r="H45" s="36" t="inlineStr">
-        <is>
-          <t>진행중</t>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="H45" s="37" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="I45" s="9" t="n"/>
@@ -2742,19 +2738,19 @@
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>4.2.4</t>
+          <t>4.2.3</t>
         </is>
       </c>
       <c r="B46" s="30" t="n"/>
       <c r="C46" s="30" t="n"/>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>통계 집계: 카메라/구역/시간 단위 Aggregation Pipeline 구성, 일별·주별·월별 지표 집계 테이블 생성</t>
+          <t>혼잡도 지표 산출: ROI별 순간 인원수, 평균 밀집도, Peak Occupancy, 혼잡도 Level 산정 기준 적용</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>통계 집계 파이프라인</t>
+          <t>혼잡도 지표 산출 모듈</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
@@ -2763,9 +2759,9 @@
         </is>
       </c>
       <c r="G46" s="15" t="n"/>
-      <c r="H46" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="H46" s="36" t="inlineStr">
+        <is>
+          <t>진행중</t>
         </is>
       </c>
       <c r="I46" s="9" t="n"/>
@@ -2793,19 +2789,19 @@
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>4.2.5</t>
+          <t>4.2.4</t>
         </is>
       </c>
       <c r="B47" s="30" t="n"/>
-      <c r="C47" s="35" t="n"/>
+      <c r="C47" s="30" t="n"/>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>대시보드 연동: WebSocket/REST API 기반 실시간 지표 송출, Front-end Chart/Heatmap/Timeline 시각화 데이터 제공</t>
+          <t>통계 집계: 카메라/구역/시간 단위 Aggregation Pipeline 구성, 일별·주별·월별 지표 집계 테이블 생성</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>대시보드 연동 API</t>
+          <t>통계 집계 파이프라인</t>
         </is>
       </c>
       <c r="F47" s="15" t="inlineStr">
@@ -2814,9 +2810,9 @@
         </is>
       </c>
       <c r="G47" s="15" t="n"/>
-      <c r="H47" s="36" t="inlineStr">
-        <is>
-          <t>진행중</t>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="I47" s="9" t="n"/>
@@ -2844,23 +2840,19 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>4.3.1</t>
+          <t>4.2.5</t>
         </is>
       </c>
       <c r="B48" s="30" t="n"/>
-      <c r="C48" s="26" t="inlineStr">
-        <is>
-          <t>폐쇄공간 잔류인원 분석</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr">
-        <is>
-          <t>폐쇄공간 모델링: 화장실·수유실·전기실 등 단일/복수 출입구 구조 정의, Entrance ROI 및 Counting Line 설정</t>
+      <c r="C48" s="35" t="n"/>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>대시보드 연동: WebSocket/REST API 기반 실시간 지표 송출, Front-end Chart/Heatmap/Timeline 시각화 데이터 제공</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>폐쇄공간 모델링 문서</t>
+          <t>대시보드 연동 API</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
@@ -2869,9 +2861,9 @@
         </is>
       </c>
       <c r="G48" s="15" t="n"/>
-      <c r="H48" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="H48" s="36" t="inlineStr">
+        <is>
+          <t>진행중</t>
         </is>
       </c>
       <c r="I48" s="9" t="n"/>
@@ -2880,12 +2872,12 @@
       <c r="L48" s="9" t="n"/>
       <c r="M48" s="9" t="n"/>
       <c r="N48" s="9" t="n"/>
-      <c r="O48" s="9" t="n"/>
-      <c r="P48" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="O48" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="P48" s="9" t="n"/>
       <c r="Q48" s="9" t="n"/>
       <c r="R48" s="9" t="n"/>
       <c r="S48" s="9" t="n"/>
@@ -2899,19 +2891,23 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>4.3.2</t>
+          <t>4.3.1</t>
         </is>
       </c>
       <c r="B49" s="30" t="n"/>
-      <c r="C49" s="30" t="n"/>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>폐쇄공간 잔류인원 분석</t>
+        </is>
+      </c>
       <c r="D49" s="14" t="inlineStr">
         <is>
-          <t>출입 방향 판별: Line Crossing Vector, Track Direction, ROI Transition 기반 IN/OUT 방향 분류</t>
+          <t>폐쇄공간 모델링: 화장실·수유실·전기실 등 단일/복수 출입구 구조 정의, Entrance ROI 및 Counting Line 설정</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>출입 방향 판별 모듈</t>
+          <t>폐쇄공간 모델링 문서</t>
         </is>
       </c>
       <c r="F49" s="15" t="inlineStr">
@@ -2919,14 +2915,10 @@
           <t>2d</t>
         </is>
       </c>
-      <c r="G49" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H49" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
+      <c r="G49" s="15" t="n"/>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="I49" s="9" t="n"/>
@@ -2954,19 +2946,19 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>4.3.3</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="B50" s="30" t="n"/>
       <c r="C50" s="30" t="n"/>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>잔류인원 산출: 누적 진입 인원과 누적 이탈 인원의 차분 기반 Current Occupancy 계산</t>
+          <t>출입 방향 판별: Line Crossing Vector, Track Direction, ROI Transition 기반 IN/OUT 방향 분류</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>잔류인원 산출 모듈</t>
+          <t>출입 방향 판별 모듈</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
@@ -3009,19 +3001,19 @@
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>4.3.4</t>
+          <t>4.3.3</t>
         </is>
       </c>
       <c r="B51" s="30" t="n"/>
       <c r="C51" s="30" t="n"/>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>카운팅 정합성 보정: Track Loss, Occlusion, ID Switch, 재진입 케이스에 대한 Counting Error 보정 로직 적용</t>
+          <t>잔류인원 산출: 누적 진입 인원과 누적 이탈 인원의 차분 기반 Current Occupancy 계산</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>카운팅 보정 모듈</t>
+          <t>잔류인원 산출 모듈</t>
         </is>
       </c>
       <c r="F51" s="15" t="inlineStr">
@@ -3029,10 +3021,14 @@
           <t>2d</t>
         </is>
       </c>
-      <c r="G51" s="15" t="n"/>
-      <c r="H51" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="H51" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="I51" s="9" t="n"/>
@@ -3060,19 +3056,19 @@
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>4.3.5</t>
+          <t>4.3.4</t>
         </is>
       </c>
       <c r="B52" s="30" t="n"/>
       <c r="C52" s="30" t="n"/>
-      <c r="D52" s="13" t="inlineStr">
-        <is>
-          <t>공간 이용 분석: 공간별 현재 잔류인원, 최대 잔류인원, 평균 체류시간, 시간대별 이용 패턴 통계 생성</t>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>카운팅 정합성 보정: Track Loss, Occlusion, ID Switch, 재진입 케이스에 대한 Counting Error 보정 로직 적용</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>공간 이용 분석 모듈</t>
+          <t>카운팅 보정 모듈</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
@@ -3111,24 +3107,24 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>4.3.6</t>
+          <t>4.3.5</t>
         </is>
       </c>
       <c r="B53" s="30" t="n"/>
-      <c r="C53" s="35" t="n"/>
+      <c r="C53" s="30" t="n"/>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>잔류 현황 연동: 폐쇄공간별 Occupancy State를 대시보드 및 2D 지도 화면에 실시간 표출</t>
+          <t>공간 이용 분석: 공간별 현재 잔류인원, 최대 잔류인원, 평균 체류시간, 시간대별 이용 패턴 통계 생성</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>잔류 현황 표출 기능</t>
+          <t>공간 이용 분석 모듈</t>
         </is>
       </c>
       <c r="F53" s="15" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="G53" s="15" t="n"/>
@@ -3162,28 +3158,24 @@
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>4.4.1</t>
+          <t>4.3.6</t>
         </is>
       </c>
       <c r="B54" s="30" t="n"/>
-      <c r="C54" s="26" t="inlineStr">
-        <is>
-          <t>2D Mapping 및 지도 연동</t>
-        </is>
-      </c>
+      <c r="C54" s="30" t="n"/>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>지도 좌표 매핑: CCTV 카메라 위치, ROI, 출입선, 분석 영역을 도면/지도 좌표계와 매핑하는 Coordinate Mapping Table 구성</t>
+          <t>잔류 현황 연동: 폐쇄공간별 Occupancy State를 대시보드 및 2D 지도 화면에 실시간 표출</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>좌표 매핑 테이블</t>
+          <t>잔류 현황 표출 기능</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="G54" s="15" t="n"/>
@@ -3217,34 +3209,26 @@
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>4.4.2</t>
+          <t>4.3.7</t>
         </is>
       </c>
       <c r="B55" s="30" t="n"/>
       <c r="C55" s="30" t="n"/>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>좌표 변환: 영상 좌표계와 2D Map 좌표계 간 Homography/Manual Calibration 기반 좌표 변환 로직 적용</t>
+          <t>비상구 고유 통과 인원: 동일 객체 반복/재진입 중복 제외, 고유 ID '최초 통과'만 유효 카운트(dedup)</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>좌표 변환 모듈</t>
-        </is>
-      </c>
-      <c r="F55" s="15" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
-      <c r="G55" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H55" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
+          <t>비상구별 고유 통과 인원 분포</t>
+        </is>
+      </c>
+      <c r="F55" s="15" t="n"/>
+      <c r="G55" s="15" t="n"/>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="I55" s="9" t="n"/>
@@ -3254,11 +3238,7 @@
       <c r="M55" s="9" t="n"/>
       <c r="N55" s="9" t="n"/>
       <c r="O55" s="9" t="n"/>
-      <c r="P55" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
       <c r="S55" s="9" t="n"/>
@@ -3272,30 +3252,26 @@
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>4.4.3</t>
+          <t>4.3.8</t>
         </is>
       </c>
       <c r="B56" s="30" t="n"/>
-      <c r="C56" s="30" t="n"/>
+      <c r="C56" s="35" t="n"/>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>구역 상태 시각화: 구역별 인원수, 혼잡도, 이동량, 잔류인원 정보를 Map Layer, Color Level, Icon Overlay 방식으로 표출</t>
+          <t>구역별 피난 개시 시점: 평균속도·평균정렬도·임계충족비율이 기준 이상 지속될 때 최초 타임스탬프 검출</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>구역 상태 시각화 기능</t>
-        </is>
-      </c>
-      <c r="F56" s="15" t="inlineStr">
-        <is>
-          <t>3d</t>
-        </is>
-      </c>
+          <t>구역별 피난 개시 timestamp</t>
+        </is>
+      </c>
+      <c r="F56" s="15" t="n"/>
       <c r="G56" s="15" t="n"/>
-      <c r="H56" s="36" t="inlineStr">
-        <is>
-          <t>진행중</t>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="I56" s="9" t="n"/>
@@ -3305,11 +3281,7 @@
       <c r="M56" s="9" t="n"/>
       <c r="N56" s="9" t="n"/>
       <c r="O56" s="9" t="n"/>
-      <c r="P56" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="P56" s="9" t="n"/>
       <c r="Q56" s="9" t="n"/>
       <c r="R56" s="9" t="n"/>
       <c r="S56" s="9" t="n"/>
@@ -3323,19 +3295,23 @@
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>4.4.4</t>
+          <t>4.4.1</t>
         </is>
       </c>
       <c r="B57" s="30" t="n"/>
-      <c r="C57" s="30" t="n"/>
-      <c r="D57" s="14" t="inlineStr">
-        <is>
-          <t>이동 흐름 표현: 카메라별 통행 방향, 주요 이동 흐름, 병목 구간을 2D 지도상 Flow Line  형태로 시각화</t>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>2D Mapping 및 지도 연동</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>지도 좌표 매핑: CCTV 카메라 위치, ROI, 출입선, 분석 영역을 도면/지도 좌표계와 매핑하는 Coordinate Mapping Table 구성</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>이동 흐름 시각화 기능</t>
+          <t>좌표 매핑 테이블</t>
         </is>
       </c>
       <c r="F57" s="15" t="inlineStr">
@@ -3344,9 +3320,9 @@
         </is>
       </c>
       <c r="G57" s="15" t="n"/>
-      <c r="H57" s="36" t="inlineStr">
-        <is>
-          <t>진행중</t>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="I57" s="9" t="n"/>
@@ -3374,19 +3350,19 @@
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>4.4.5</t>
+          <t>4.4.2</t>
         </is>
       </c>
       <c r="B58" s="30" t="n"/>
-      <c r="C58" s="35" t="n"/>
-      <c r="D58" s="14" t="inlineStr">
-        <is>
-          <t>데이터 동기화: 실시간 분석 결과와 지도 객체 간 Binding Key 구성, 카메라 ID/구역 ID 기반 상태 업데이트 구조 설계</t>
-        </is>
-      </c>
-      <c r="E58" s="14" t="inlineStr">
-        <is>
-          <t>데이터 동기화 모듈</t>
+      <c r="C58" s="30" t="n"/>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>좌표 변환: 영상 좌표계와 2D Map 좌표계 간 Homography/Manual Calibration 기반 좌표 변환 로직 적용</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>좌표 변환 모듈</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
@@ -3394,10 +3370,14 @@
           <t>2d</t>
         </is>
       </c>
-      <c r="G58" s="15" t="n"/>
-      <c r="H58" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="G58" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="H58" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="I58" s="9" t="n"/>
@@ -3425,34 +3405,30 @@
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>4.5.1</t>
+          <t>4.4.3</t>
         </is>
       </c>
       <c r="B59" s="30" t="n"/>
-      <c r="C59" s="26" t="inlineStr">
-        <is>
-          <t>지도 기반 대피 경로 제공</t>
-        </is>
-      </c>
-      <c r="D59" s="14" t="inlineStr">
-        <is>
-          <t>대피 경로 데이터 모델링: 출입구, 계단, 통로, 승강장, 대합실 등 공간 노드를 Graph 구조로 정의</t>
+      <c r="C59" s="30" t="n"/>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>구역 상태 시각화: 구역별 인원수, 혼잡도, 이동량, 잔류인원 정보를 Map Layer, Color Level, Icon Overlay 방식으로 표출</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>대피 경로 Graph 모델</t>
+          <t>구역 상태 시각화 기능</t>
         </is>
       </c>
       <c r="F59" s="15" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="G59" s="15" t="n"/>
-      <c r="H59" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="H59" s="36" t="inlineStr">
+        <is>
+          <t>진행중</t>
         </is>
       </c>
       <c r="I59" s="9" t="n"/>
@@ -3462,12 +3438,12 @@
       <c r="M59" s="9" t="n"/>
       <c r="N59" s="9" t="n"/>
       <c r="O59" s="9" t="n"/>
-      <c r="P59" s="9" t="n"/>
-      <c r="Q59" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="P59" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Q59" s="9" t="n"/>
       <c r="R59" s="9" t="n"/>
       <c r="S59" s="9" t="n"/>
       <c r="T59" s="9" t="n"/>
@@ -3480,19 +3456,19 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>4.5.2</t>
+          <t>4.4.4</t>
         </is>
       </c>
       <c r="B60" s="30" t="n"/>
       <c r="C60" s="30" t="n"/>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>경로 탐색 로직: Node-Edge 기반 Shortest Path/Dijkstra 또는 Weighted Path 탐색 로직 적용</t>
+          <t>이동 흐름 표현: 카메라별 통행 방향, 주요 이동 흐름, 병목 구간을 2D 지도상 Flow Line  형태로 시각화</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>경로 탐색 알고리즘</t>
+          <t>이동 흐름 시각화 기능</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
@@ -3501,9 +3477,9 @@
         </is>
       </c>
       <c r="G60" s="15" t="n"/>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="H60" s="36" t="inlineStr">
+        <is>
+          <t>진행중</t>
         </is>
       </c>
       <c r="I60" s="9" t="n"/>
@@ -3513,12 +3489,12 @@
       <c r="M60" s="9" t="n"/>
       <c r="N60" s="9" t="n"/>
       <c r="O60" s="9" t="n"/>
-      <c r="P60" s="9" t="n"/>
-      <c r="Q60" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="P60" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Q60" s="9" t="n"/>
       <c r="R60" s="9" t="n"/>
       <c r="S60" s="9" t="n"/>
       <c r="T60" s="9" t="n"/>
@@ -3531,19 +3507,19 @@
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>4.5.3</t>
+          <t>4.4.5</t>
         </is>
       </c>
       <c r="B61" s="30" t="n"/>
-      <c r="C61" s="30" t="n"/>
+      <c r="C61" s="35" t="n"/>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>혼잡도 기반 가중치 적용: 구역별 실시간 인원수, 밀집도, 통행량을 Edge Weight로 반영하여 대피 경로 후보 산출</t>
+          <t>데이터 동기화: 실시간 분석 결과와 지도 객체 간 Binding Key 구성, 카메라 ID/구역 ID 기반 상태 업데이트 구조 설계</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>혼잡도 기반 가중치 모듈</t>
+          <t>데이터 동기화 모듈</t>
         </is>
       </c>
       <c r="F61" s="15" t="inlineStr">
@@ -3564,12 +3540,12 @@
       <c r="M61" s="9" t="n"/>
       <c r="N61" s="9" t="n"/>
       <c r="O61" s="9" t="n"/>
-      <c r="P61" s="9" t="n"/>
-      <c r="Q61" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="P61" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Q61" s="9" t="n"/>
       <c r="R61" s="9" t="n"/>
       <c r="S61" s="9" t="n"/>
       <c r="T61" s="9" t="n"/>
@@ -3582,19 +3558,23 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>4.5.4</t>
+          <t>4.5.1</t>
         </is>
       </c>
       <c r="B62" s="30" t="n"/>
-      <c r="C62" s="30" t="n"/>
+      <c r="C62" s="26" t="inlineStr">
+        <is>
+          <t>지도 기반 대피 경로 제공</t>
+        </is>
+      </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>대피 경로 시각화: 2D Map 상에 추천 경로, 대체 경로, 병목 구간을 Layer Overlay 방식으로 표출</t>
+          <t>대피 경로 데이터 모델링: 출입구, 계단, 통로, 승강장, 대합실 등 공간 노드를 Graph 구조로 정의</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>대피 경로 시각화 기능</t>
+          <t>대피 경로 Graph 모델</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
@@ -3603,9 +3583,9 @@
         </is>
       </c>
       <c r="G62" s="15" t="n"/>
-      <c r="H62" s="36" t="inlineStr">
-        <is>
-          <t>진행중</t>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="I62" s="9" t="n"/>
@@ -3633,19 +3613,19 @@
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>4.5.5</t>
+          <t>4.5.2</t>
         </is>
       </c>
       <c r="B63" s="30" t="n"/>
-      <c r="C63" s="35" t="n"/>
+      <c r="C63" s="30" t="n"/>
       <c r="D63" s="14" t="inlineStr">
         <is>
-          <t>경로 검증: 현장 도면 기준 이동 가능 구간, 폐쇄 구간, 출입 제한 구역 반영 및 운영자 검토용 경로 검증 데이터 생성</t>
+          <t>경로 탐색 로직: Node-Edge 기반 Shortest Path/Dijkstra 또는 Weighted Path 탐색 로직 적용</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>경로 검증 보고서</t>
+          <t>경로 탐색 알고리즘</t>
         </is>
       </c>
       <c r="F63" s="15" t="inlineStr">
@@ -3684,23 +3664,19 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>4.6.1</t>
+          <t>4.5.3</t>
         </is>
       </c>
       <c r="B64" s="30" t="n"/>
-      <c r="C64" s="27" t="inlineStr">
-        <is>
-          <t>고객사 보고서 초안 제공</t>
-        </is>
-      </c>
-      <c r="D64" s="13" t="inlineStr">
-        <is>
-          <t>분석 데이터 마트 구성: 이동량, 체류시간, 혼잡도, 잔류인원, 구역별 통계 데이터를 Report Mart 형태로 정규화</t>
-        </is>
-      </c>
-      <c r="E64" s="13" t="inlineStr">
-        <is>
-          <t>Report Mart 스키마</t>
+      <c r="C64" s="30" t="n"/>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>혼잡도 기반 가중치 적용: 구역별 실시간 인원수, 밀집도, 통행량을 Edge Weight로 반영하여 대피 경로 후보 산출</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>혼잡도 기반 가중치 모듈</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
@@ -3739,19 +3715,19 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>4.6.2</t>
+          <t>4.5.4</t>
         </is>
       </c>
       <c r="B65" s="30" t="n"/>
       <c r="C65" s="30" t="n"/>
       <c r="D65" s="14" t="inlineStr">
         <is>
-          <t>보고서 지표 자동 산출:  KPI, Peak Time, Top Congestion Zone, Closed-space Occupancy Summary 자동 계산</t>
+          <t>대피 경로 시각화: 2D Map 상에 추천 경로, 대체 경로, 병목 구간을 Layer Overlay 방식으로 표출</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>보고서 KPI 산출 모듈</t>
+          <t>대피 경로 시각화 기능</t>
         </is>
       </c>
       <c r="F65" s="15" t="inlineStr">
@@ -3760,9 +3736,9 @@
         </is>
       </c>
       <c r="G65" s="15" t="n"/>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="H65" s="36" t="inlineStr">
+        <is>
+          <t>진행중</t>
         </is>
       </c>
       <c r="I65" s="9" t="n"/>
@@ -3790,19 +3766,19 @@
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>4.6.3</t>
+          <t>4.5.5</t>
         </is>
       </c>
       <c r="B66" s="30" t="n"/>
-      <c r="C66" s="30" t="n"/>
+      <c r="C66" s="35" t="n"/>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>시각자료 생성: Chart, Heatmap, Map Capture 기반 보고서 삽입용 시각자료 자동 생성</t>
+          <t>경로 검증: 현장 도면 기준 이동 가능 구간, 폐쇄 구간, 출입 제한 구역 반영 및 운영자 검토용 경로 검증 데이터 생성</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>시각자료 생성 모듈</t>
+          <t>경로 검증 보고서</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
@@ -3841,24 +3817,28 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>4.6.4</t>
+          <t>4.6.1</t>
         </is>
       </c>
       <c r="B67" s="30" t="n"/>
-      <c r="C67" s="30" t="n"/>
+      <c r="C67" s="27" t="inlineStr">
+        <is>
+          <t>고객사 보고서 초안 제공</t>
+        </is>
+      </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>보고서 초안 생성: 고객사 제출용 운영 분석 보고서 Template 구성, 주요 지표 요약 및 구역별 분석 Comment 자동 생성</t>
+          <t>분석 데이터 마트 구성: 이동량, 체류시간, 혼잡도, 잔류인원, 구역별 통계 데이터를 Report Mart 형태로 정규화</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>보고서 Template 및 생성기</t>
+          <t>Report Mart 스키마</t>
         </is>
       </c>
       <c r="F67" s="15" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="G67" s="15" t="n"/>
@@ -3892,19 +3872,19 @@
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>4.6.5</t>
-        </is>
-      </c>
-      <c r="B68" s="35" t="n"/>
-      <c r="C68" s="35" t="n"/>
-      <c r="D68" s="13" t="inlineStr">
-        <is>
-          <t>파일 출력: PDF/Excel/PPT 형식 Export 구조 설계, 보고서 이력 저장 및 재생성 기능 구성</t>
+          <t>4.6.2</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="n"/>
+      <c r="C68" s="30" t="n"/>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>보고서 지표 자동 산출:  KPI, Peak Time, Top Congestion Zone, Closed-space Occupancy Summary 자동 계산</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>보고서 Export 모듈</t>
+          <t>보고서 KPI 산출 모듈</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
@@ -3941,55 +3921,47 @@
       <c r="Y68" s="9" t="n"/>
     </row>
     <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>5.1.1</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>대시보드 및 리포트 개발</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
-        <is>
-          <t>실시간 관제 화면 개발</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>인원 현황 시각화: D3.js/ECharts 기반 실시간 차트, WebGL 렌더링, 1초 갱신 주기</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>실시간 인원 현황 대시보드 (D3.js)</t>
-        </is>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>4.6.3</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="n"/>
+      <c r="C69" s="30" t="n"/>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>시각자료 생성: Chart, Heatmap, Map Capture 기반 보고서 삽입용 시각자료 자동 생성</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>시각자료 생성 모듈</t>
+        </is>
+      </c>
+      <c r="F69" s="15" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="G69" s="10" t="n"/>
-      <c r="H69" s="36" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="I69" s="8" t="n"/>
+      <c r="G69" s="15" t="n"/>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="n"/>
       <c r="J69" s="9" t="n"/>
       <c r="K69" s="9" t="n"/>
       <c r="L69" s="9" t="n"/>
       <c r="M69" s="9" t="n"/>
-      <c r="N69" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="N69" s="9" t="n"/>
       <c r="O69" s="9" t="n"/>
       <c r="P69" s="9" t="n"/>
-      <c r="Q69" s="9" t="n"/>
+      <c r="Q69" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="R69" s="9" t="n"/>
       <c r="S69" s="9" t="n"/>
       <c r="T69" s="9" t="n"/>
@@ -4000,47 +3972,47 @@
       <c r="Y69" s="9" t="n"/>
     </row>
     <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>5.1.2</t>
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>4.6.4</t>
         </is>
       </c>
       <c r="B70" s="30" t="n"/>
       <c r="C70" s="30" t="n"/>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>혼잡도 표시: 층별 평면도 오버레이, 색상 그라데이션(Green→Yellow→Red), 애니메이션 전환</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>층별 혼잡도 시각화 화면</t>
-        </is>
-      </c>
-      <c r="F70" s="10" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
-      <c r="G70" s="10" t="n"/>
-      <c r="H70" s="36" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="I70" s="8" t="n"/>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>보고서 초안 생성: 고객사 제출용 운영 분석 보고서 Template 구성, 주요 지표 요약 및 구역별 분석 Comment 자동 생성</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>보고서 Template 및 생성기</t>
+        </is>
+      </c>
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>3d</t>
+        </is>
+      </c>
+      <c r="G70" s="15" t="n"/>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="n"/>
       <c r="J70" s="9" t="n"/>
       <c r="K70" s="9" t="n"/>
       <c r="L70" s="9" t="n"/>
       <c r="M70" s="9" t="n"/>
-      <c r="N70" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="N70" s="9" t="n"/>
       <c r="O70" s="9" t="n"/>
       <c r="P70" s="9" t="n"/>
-      <c r="Q70" s="9" t="n"/>
+      <c r="Q70" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="R70" s="9" t="n"/>
       <c r="S70" s="9" t="n"/>
       <c r="T70" s="9" t="n"/>
@@ -4051,47 +4023,47 @@
       <c r="Y70" s="9" t="n"/>
     </row>
     <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>5.1.3</t>
-        </is>
-      </c>
-      <c r="B71" s="30" t="n"/>
-      <c r="C71" s="30" t="n"/>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>경보 화면: Toast 알림, 사운드 경고, 이벤트 타임라인, 영상 팝업 재생</t>
-        </is>
-      </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>이벤트 경보 및 알림 UI</t>
-        </is>
-      </c>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>4.6.5</t>
+        </is>
+      </c>
+      <c r="B71" s="35" t="n"/>
+      <c r="C71" s="35" t="n"/>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>파일 출력: PDF/Excel/PPT 형식 Export 구조 설계, 보고서 이력 저장 및 재생성 기능 구성</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>보고서 Export 모듈</t>
+        </is>
+      </c>
+      <c r="F71" s="15" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="G71" s="10" t="n"/>
+      <c r="G71" s="15" t="n"/>
       <c r="H71" s="9" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I71" s="8" t="n"/>
+      <c r="I71" s="9" t="n"/>
       <c r="J71" s="9" t="n"/>
       <c r="K71" s="9" t="n"/>
       <c r="L71" s="9" t="n"/>
       <c r="M71" s="9" t="n"/>
-      <c r="N71" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="N71" s="9" t="n"/>
       <c r="O71" s="9" t="n"/>
       <c r="P71" s="9" t="n"/>
-      <c r="Q71" s="9" t="n"/>
+      <c r="Q71" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="R71" s="9" t="n"/>
       <c r="S71" s="9" t="n"/>
       <c r="T71" s="9" t="n"/>
@@ -4104,19 +4076,27 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>5.1.4</t>
-        </is>
-      </c>
-      <c r="B72" s="30" t="n"/>
-      <c r="C72" s="35" t="n"/>
+          <t>5.1.1</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>대시보드 및 리포트 개발</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>실시간 관제 화면 개발</t>
+        </is>
+      </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>관리자 UI: 사용자 관리, 카메라 설정, 임계값 조정, 시스템 로그 조회</t>
+          <t>인원 현황 시각화: D3.js/ECharts 기반 실시간 차트, WebGL 렌더링, 1초 갱신 주기</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>관리자 설정 및 시스템 관리 UI</t>
+          <t>실시간 인원 현황 대시보드 (D3.js)</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -4125,9 +4105,9 @@
         </is>
       </c>
       <c r="G72" s="10" t="n"/>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="H72" s="36" t="inlineStr">
+        <is>
+          <t>진행중</t>
         </is>
       </c>
       <c r="I72" s="8" t="n"/>
@@ -4155,23 +4135,19 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>5.2.1</t>
+          <t>5.1.2</t>
         </is>
       </c>
       <c r="B73" s="30" t="n"/>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>분석 리포트 기능 개발</t>
-        </is>
-      </c>
+      <c r="C73" s="30" t="n"/>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>KPI 산출: Apache Spark 배치 처리, 일/주/월 집계, 자동 리포트 생성(PDF/Excel)</t>
+          <t>혼잡도 표시: 층별 평면도 오버레이, 색상 그라데이션(Green→Yellow→Red), 애니메이션 전환</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>KPI 자동 산출 배치 모듈 (Spark)</t>
+          <t>층별 혼잡도 시각화 화면</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -4180,9 +4156,9 @@
         </is>
       </c>
       <c r="G73" s="10" t="n"/>
-      <c r="H73" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="H73" s="36" t="inlineStr">
+        <is>
+          <t>진행중</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -4190,12 +4166,12 @@
       <c r="K73" s="9" t="n"/>
       <c r="L73" s="9" t="n"/>
       <c r="M73" s="9" t="n"/>
-      <c r="N73" s="9" t="n"/>
-      <c r="O73" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="O73" s="9" t="n"/>
       <c r="P73" s="9" t="n"/>
       <c r="Q73" s="9" t="n"/>
       <c r="R73" s="9" t="n"/>
@@ -4210,19 +4186,19 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>5.2.2</t>
+          <t>5.1.3</t>
         </is>
       </c>
       <c r="B74" s="30" t="n"/>
       <c r="C74" s="30" t="n"/>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>히트맵 시각화: Heatmap.js, 시간별 밀집 패턴, 동선 궤적 오버레이, 재생 기능</t>
+          <t>경보 화면: Toast 알림, 사운드 경고, 이벤트 타임라인, 영상 팝업 재생</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>동선 히트맵 시각화 모듈</t>
+          <t>이벤트 경보 및 알림 UI</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -4241,12 +4217,12 @@
       <c r="K74" s="9" t="n"/>
       <c r="L74" s="9" t="n"/>
       <c r="M74" s="9" t="n"/>
-      <c r="N74" s="9" t="n"/>
-      <c r="O74" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="N74" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="O74" s="9" t="n"/>
       <c r="P74" s="9" t="n"/>
       <c r="Q74" s="9" t="n"/>
       <c r="R74" s="9" t="n"/>
@@ -4261,19 +4237,19 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>5.2.3</t>
+          <t>5.1.4</t>
         </is>
       </c>
       <c r="B75" s="30" t="n"/>
-      <c r="C75" s="30" t="n"/>
+      <c r="C75" s="35" t="n"/>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>비교 리포트: 회차별 KPI 테이블, 개선율 그래프, 통계적 유의성 검정(t-test)</t>
+          <t>관리자 UI: 사용자 관리, 카메라 설정, 임계값 조정, 시스템 로그 조회</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>회차별 비교 리포트 생성기</t>
+          <t>관리자 설정 및 시스템 관리 UI</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -4292,12 +4268,12 @@
       <c r="K75" s="9" t="n"/>
       <c r="L75" s="9" t="n"/>
       <c r="M75" s="9" t="n"/>
-      <c r="N75" s="9" t="n"/>
-      <c r="O75" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="N75" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="O75" s="9" t="n"/>
       <c r="P75" s="9" t="n"/>
       <c r="Q75" s="9" t="n"/>
       <c r="R75" s="9" t="n"/>
@@ -4312,19 +4288,23 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>5.2.4</t>
-        </is>
-      </c>
-      <c r="B76" s="35" t="n"/>
-      <c r="C76" s="35" t="n"/>
+          <t>5.2.1</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="n"/>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>분석 리포트 기능 개발</t>
+        </is>
+      </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>로그 저장: Elasticsearch 인덱싱, Kibana 대시보드, 90일 보존 정책, 압축 아카이빙</t>
-        </is>
-      </c>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이벤트 로그 저장 및 검색 시스템 </t>
+          <t>KPI 산출: Apache Spark 배치 처리, 일/주/월 집계, 자동 리포트 생성(PDF/Excel)</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>KPI 자동 산출 배치 모듈 (Spark)</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -4363,32 +4343,24 @@
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>6.1.1</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>현장 실증 및 성능 검증</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t>현장 실증 수행</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>현장 테스트: 피난훈련  수행, 50/100/200인 규모 파악</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>현장 테스트</t>
+          <t>5.2.2</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="n"/>
+      <c r="C77" s="30" t="n"/>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>히트맵 시각화: Heatmap.js, 시간별 밀집 패턴, 동선 궤적 오버레이, 재생 기능</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>동선 히트맵 시각화 모듈</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>1w</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="G77" s="10" t="n"/>
@@ -4403,14 +4375,14 @@
       <c r="L77" s="9" t="n"/>
       <c r="M77" s="9" t="n"/>
       <c r="N77" s="9" t="n"/>
-      <c r="O77" s="9" t="n"/>
+      <c r="O77" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="P77" s="9" t="n"/>
       <c r="Q77" s="9" t="n"/>
-      <c r="R77" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="R77" s="9" t="n"/>
       <c r="S77" s="9" t="n"/>
       <c r="T77" s="9" t="n"/>
       <c r="U77" s="9" t="n"/>
@@ -4422,24 +4394,24 @@
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>5.2.3</t>
         </is>
       </c>
       <c r="B78" s="30" t="n"/>
       <c r="C78" s="30" t="n"/>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>시나리오별 검증: 정상 대피, 병목 발생, 역류 상황, 복합 이상상황 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>시나리오별 기능 검증</t>
+          <t>비교 리포트: 회차별 KPI 테이블, 개선율 그래프, 통계적 유의성 검정(t-test)</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>회차별 비교 리포트 생성기</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>1w</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="G78" s="10" t="n"/>
@@ -4454,15 +4426,15 @@
       <c r="L78" s="9" t="n"/>
       <c r="M78" s="9" t="n"/>
       <c r="N78" s="9" t="n"/>
-      <c r="O78" s="9" t="n"/>
+      <c r="O78" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="P78" s="9" t="n"/>
       <c r="Q78" s="9" t="n"/>
       <c r="R78" s="9" t="n"/>
-      <c r="S78" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="S78" s="9" t="n"/>
       <c r="T78" s="9" t="n"/>
       <c r="U78" s="9" t="n"/>
       <c r="V78" s="9" t="n"/>
@@ -4473,24 +4445,24 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>6.1.3</t>
-        </is>
-      </c>
-      <c r="B79" s="30" t="n"/>
-      <c r="C79" s="30" t="n"/>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>피드백 수집: 운영자 인터뷰,  UI/UX 개선사항 도출</t>
+          <t>5.2.4</t>
+        </is>
+      </c>
+      <c r="B79" s="35" t="n"/>
+      <c r="C79" s="35" t="n"/>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>로그 저장: Elasticsearch 인덱싱, Kibana 대시보드, 90일 보존 정책, 압축 아카이빙</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>운영자 피드백</t>
+          <t xml:space="preserve">이벤트 로그 저장 및 검색 시스템 </t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>1w</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="G79" s="10" t="n"/>
@@ -4505,16 +4477,16 @@
       <c r="L79" s="9" t="n"/>
       <c r="M79" s="9" t="n"/>
       <c r="N79" s="9" t="n"/>
-      <c r="O79" s="9" t="n"/>
+      <c r="O79" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="P79" s="9" t="n"/>
       <c r="Q79" s="9" t="n"/>
       <c r="R79" s="9" t="n"/>
       <c r="S79" s="9" t="n"/>
-      <c r="T79" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="T79" s="9" t="n"/>
       <c r="U79" s="9" t="n"/>
       <c r="V79" s="9" t="n"/>
       <c r="W79" s="9" t="n"/>
@@ -4524,19 +4496,27 @@
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>6.1.4</t>
-        </is>
-      </c>
-      <c r="B80" s="30" t="n"/>
-      <c r="C80" s="35" t="n"/>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>병목구간 분석: 이벤트 로그 기반 병목 빈도, 위치, 지속시간 분석, 개선 우선순위 도출</t>
+          <t>6.1.1</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>현장 실증 및 성능 검증</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>현장 실증 수행</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>현장 테스트: 피난훈련  수행, 50/100/200인 규모 파악</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>병목구간 분석</t>
+          <t>현장 테스트</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
@@ -4559,14 +4539,14 @@
       <c r="O80" s="9" t="n"/>
       <c r="P80" s="9" t="n"/>
       <c r="Q80" s="9" t="n"/>
-      <c r="R80" s="9" t="n"/>
+      <c r="R80" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="S80" s="9" t="n"/>
       <c r="T80" s="9" t="n"/>
-      <c r="U80" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="U80" s="9" t="n"/>
       <c r="V80" s="9" t="n"/>
       <c r="W80" s="9" t="n"/>
       <c r="X80" s="9" t="n"/>
@@ -4575,28 +4555,24 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>6.2.1</t>
+          <t>6.1.2</t>
         </is>
       </c>
       <c r="B81" s="30" t="n"/>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t>성능 검증 및 최적화</t>
-        </is>
-      </c>
+      <c r="C81" s="30" t="n"/>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>탐지 정확도 검증: Precision/Recall/F1-score 측정, Confusion Matrix, 오탐/미탐 사례 분석</t>
+          <t>시나리오별 검증: 정상 대피, 병목 발생, 역류 상황, 복합 이상상황 시뮬레이션</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>탐지 정확도 검증</t>
+          <t>시나리오별 기능 검증</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>2w</t>
+          <t>1w</t>
         </is>
       </c>
       <c r="G81" s="10" t="n"/>
@@ -4612,18 +4588,14 @@
       <c r="M81" s="9" t="n"/>
       <c r="N81" s="9" t="n"/>
       <c r="O81" s="9" t="n"/>
-      <c r="P81" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="Q81" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="P81" s="9" t="n"/>
+      <c r="Q81" s="9" t="n"/>
       <c r="R81" s="9" t="n"/>
-      <c r="S81" s="9" t="n"/>
+      <c r="S81" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="T81" s="9" t="n"/>
       <c r="U81" s="9" t="n"/>
       <c r="V81" s="9" t="n"/>
@@ -4634,24 +4606,24 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>6.2.2</t>
+          <t>6.1.3</t>
         </is>
       </c>
       <c r="B82" s="30" t="n"/>
       <c r="C82" s="30" t="n"/>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>이벤트 탐지 검증: 이벤트별 탐지율, 평균 탐지 지연시간, False Positive Rate 측정</t>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>피드백 수집: 운영자 인터뷰,  UI/UX 개선사항 도출</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>이벤트 탐지 성능 검증</t>
+          <t>운영자 피드백</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>2w</t>
+          <t>1w</t>
         </is>
       </c>
       <c r="G82" s="10" t="n"/>
@@ -4667,19 +4639,15 @@
       <c r="M82" s="9" t="n"/>
       <c r="N82" s="9" t="n"/>
       <c r="O82" s="9" t="n"/>
-      <c r="P82" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="Q82" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="P82" s="9" t="n"/>
+      <c r="Q82" s="9" t="n"/>
       <c r="R82" s="9" t="n"/>
       <c r="S82" s="9" t="n"/>
-      <c r="T82" s="9" t="n"/>
+      <c r="T82" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="U82" s="9" t="n"/>
       <c r="V82" s="9" t="n"/>
       <c r="W82" s="9" t="n"/>
@@ -4689,24 +4657,24 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>6.2.3</t>
+          <t>6.1.4</t>
         </is>
       </c>
       <c r="B83" s="30" t="n"/>
-      <c r="C83" s="30" t="n"/>
+      <c r="C83" s="35" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>오탐/미탐 분석: 오탐 원인(조명, 반사, 그림자), 미탐 원인(가림, 밀집), 개선 방안 도출</t>
+          <t>병목구간 분석: 이벤트 로그 기반 병목 빈도, 위치, 지속시간 분석, 개선 우선순위 도출</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>오탐/미탐 원인 분석</t>
+          <t>병목구간 분석</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>2w</t>
+          <t>1w</t>
         </is>
       </c>
       <c r="G83" s="10" t="n"/>
@@ -4722,20 +4690,16 @@
       <c r="M83" s="9" t="n"/>
       <c r="N83" s="9" t="n"/>
       <c r="O83" s="9" t="n"/>
-      <c r="P83" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="Q83" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="P83" s="9" t="n"/>
+      <c r="Q83" s="9" t="n"/>
       <c r="R83" s="9" t="n"/>
       <c r="S83" s="9" t="n"/>
       <c r="T83" s="9" t="n"/>
-      <c r="U83" s="9" t="n"/>
+      <c r="U83" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="V83" s="9" t="n"/>
       <c r="W83" s="9" t="n"/>
       <c r="X83" s="9" t="n"/>
@@ -4744,19 +4708,23 @@
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>6.2.4</t>
+          <t>6.2.1</t>
         </is>
       </c>
       <c r="B84" s="30" t="n"/>
-      <c r="C84" s="35" t="n"/>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>성능 검증 및 최적화</t>
+        </is>
+      </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>서버 안정성: 24시간 연속 운영 테스트, CPU/GPU 사용률, 메모리 누수, OOM 발생 여부</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>24시간 안정성 테스트</t>
+          <t>탐지 정확도 검증: Precision/Recall/F1-score 측정, Confusion Matrix, 오탐/미탐 사례 분석</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>탐지 정확도 검증</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
@@ -4799,28 +4767,24 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>6.3.1</t>
+          <t>6.2.2</t>
         </is>
       </c>
       <c r="B85" s="30" t="n"/>
-      <c r="C85" s="8" t="inlineStr">
-        <is>
-          <t>기능 안정화 및 운영 최적화</t>
-        </is>
-      </c>
+      <c r="C85" s="30" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>기능 개선: 현장 이슈 기반 핫픽스, 모델 재학습, 임계값 재조정</t>
+          <t>이벤트 탐지 검증: 이벤트별 탐지율, 평균 탐지 지연시간, False Positive Rate 측정</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">현장 이슈 기반 핫픽스 </t>
+          <t>이벤트 탐지 성능 검증</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>2w</t>
         </is>
       </c>
       <c r="G85" s="10" t="n"/>
@@ -4836,17 +4800,21 @@
       <c r="M85" s="9" t="n"/>
       <c r="N85" s="9" t="n"/>
       <c r="O85" s="9" t="n"/>
-      <c r="P85" s="9" t="n"/>
-      <c r="Q85" s="9" t="n"/>
+      <c r="P85" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Q85" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="R85" s="9" t="n"/>
       <c r="S85" s="9" t="n"/>
       <c r="T85" s="9" t="n"/>
       <c r="U85" s="9" t="n"/>
-      <c r="V85" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="V85" s="9" t="n"/>
       <c r="W85" s="9" t="n"/>
       <c r="X85" s="9" t="n"/>
       <c r="Y85" s="9" t="n"/>
@@ -4854,24 +4822,24 @@
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>6.3.2</t>
+          <t>6.2.3</t>
         </is>
       </c>
       <c r="B86" s="30" t="n"/>
       <c r="C86" s="30" t="n"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>성능 튜닝: TensorRT 최적화, Batch Size 조정, 멀티스레딩, 메모리 풀링</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>TensorRT 최적화 성능 개선</t>
+          <t>오탐/미탐 분석: 오탐 원인(조명, 반사, 그림자), 미탐 원인(가림, 밀집), 개선 방안 도출</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>오탐/미탐 원인 분석</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>2w</t>
         </is>
       </c>
       <c r="G86" s="10" t="n"/>
@@ -4887,17 +4855,21 @@
       <c r="M86" s="9" t="n"/>
       <c r="N86" s="9" t="n"/>
       <c r="O86" s="9" t="n"/>
-      <c r="P86" s="9" t="n"/>
-      <c r="Q86" s="9" t="n"/>
+      <c r="P86" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Q86" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="R86" s="9" t="n"/>
       <c r="S86" s="9" t="n"/>
       <c r="T86" s="9" t="n"/>
       <c r="U86" s="9" t="n"/>
-      <c r="V86" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="V86" s="9" t="n"/>
       <c r="W86" s="9" t="n"/>
       <c r="X86" s="9" t="n"/>
       <c r="Y86" s="9" t="n"/>
@@ -4905,24 +4877,24 @@
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>6.3.3</t>
+          <t>6.2.4</t>
         </is>
       </c>
       <c r="B87" s="30" t="n"/>
-      <c r="C87" s="30" t="n"/>
+      <c r="C87" s="35" t="n"/>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>UI 보완: 사용자 피드백 반영, 반응형 레이아웃, 접근성(A11y) 개선</t>
+          <t>서버 안정성: 24시간 연속 운영 테스트, CPU/GPU 사용률, 메모리 누수, OOM 발생 여부</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>UI/UX 개선 적용</t>
+          <t>24시간 안정성 테스트</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>2w</t>
         </is>
       </c>
       <c r="G87" s="10" t="n"/>
@@ -4938,37 +4910,45 @@
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="9" t="n"/>
       <c r="O87" s="9" t="n"/>
-      <c r="P87" s="9" t="n"/>
-      <c r="Q87" s="9" t="n"/>
+      <c r="P87" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Q87" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="R87" s="9" t="n"/>
       <c r="S87" s="9" t="n"/>
       <c r="T87" s="9" t="n"/>
       <c r="U87" s="9" t="n"/>
       <c r="V87" s="9" t="n"/>
-      <c r="W87" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="W87" s="9" t="n"/>
       <c r="X87" s="9" t="n"/>
       <c r="Y87" s="9" t="n"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>6.3.4</t>
-        </is>
-      </c>
-      <c r="B88" s="35" t="n"/>
-      <c r="C88" s="35" t="n"/>
+          <t>6.3.1</t>
+        </is>
+      </c>
+      <c r="B88" s="30" t="n"/>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>기능 안정화 및 운영 최적화</t>
+        </is>
+      </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>통합 테스트: End-to-End 시나리오, 부하 테스트(Locust), 장애 복구(Failover) 검증</t>
-        </is>
-      </c>
-      <c r="E88" s="8" t="inlineStr">
-        <is>
-          <t>E2E 통합 테스트 및 부하 테스트</t>
+          <t>기능 개선: 현장 이슈 기반 핫픽스, 모델 재학습, 임계값 재조정</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현장 이슈 기반 핫픽스 </t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
@@ -4995,39 +4975,31 @@
       <c r="S88" s="9" t="n"/>
       <c r="T88" s="9" t="n"/>
       <c r="U88" s="9" t="n"/>
-      <c r="V88" s="9" t="n"/>
-      <c r="W88" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="V88" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W88" s="9" t="n"/>
       <c r="X88" s="9" t="n"/>
       <c r="Y88" s="9" t="n"/>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>7.1.1</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>결과 정리 및 최종 보고</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>결과 분석 및 개선안 도출</t>
-        </is>
-      </c>
+          <t>6.3.2</t>
+        </is>
+      </c>
+      <c r="B89" s="30" t="n"/>
+      <c r="C89" s="30" t="n"/>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>데이터 분석: Pandas/NumPy 기반 통계 분석, 회차별 KPI 비교, 개선율 산출</t>
-        </is>
-      </c>
-      <c r="E89" s="11" t="inlineStr">
-        <is>
-          <t>훈련 데이터 통계 분석 보고서</t>
+          <t>성능 튜닝: TensorRT 최적화, Batch Size 조정, 멀티스레딩, 메모리 풀링</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>TensorRT 최적화 성능 개선</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
@@ -5054,31 +5026,31 @@
       <c r="S89" s="9" t="n"/>
       <c r="T89" s="9" t="n"/>
       <c r="U89" s="9" t="n"/>
-      <c r="V89" s="9" t="n"/>
-      <c r="W89" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="V89" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W89" s="9" t="n"/>
       <c r="X89" s="9" t="n"/>
       <c r="Y89" s="9" t="n"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>7.1.2</t>
+          <t>6.3.3</t>
         </is>
       </c>
       <c r="B90" s="30" t="n"/>
       <c r="C90" s="30" t="n"/>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>위험구간 분석: 병목 발생 Top 5 구간, 시간대별 패턴, 물리적 개선 권고사항</t>
-        </is>
-      </c>
-      <c r="E90" s="11" t="inlineStr">
-        <is>
-          <t>위험구간 분석</t>
+          <t>UI 보완: 사용자 피드백 반영, 반응형 레이아웃, 접근성(A11y) 개선</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>UI/UX 개선 적용</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
@@ -5117,24 +5089,24 @@
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>7.1.3</t>
-        </is>
-      </c>
-      <c r="B91" s="30" t="n"/>
-      <c r="C91" s="30" t="n"/>
+          <t>6.3.4</t>
+        </is>
+      </c>
+      <c r="B91" s="35" t="n"/>
+      <c r="C91" s="35" t="n"/>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>개선 방향: 모델 고도화 로드맵, 인프라 확장 계획, 운영 프로세스 개선안</t>
-        </is>
-      </c>
-      <c r="E91" s="11" t="inlineStr">
-        <is>
-          <t>기술 고도화 로드맵</t>
+          <t>통합 테스트: End-to-End 시나리오, 부하 테스트(Locust), 장애 복구(Failover) 검증</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>E2E 통합 테스트 및 부하 테스트</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="G91" s="10" t="n"/>
@@ -5157,30 +5129,38 @@
       <c r="T91" s="9" t="n"/>
       <c r="U91" s="9" t="n"/>
       <c r="V91" s="9" t="n"/>
-      <c r="W91" s="9" t="n"/>
-      <c r="X91" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="W91" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="X91" s="9" t="n"/>
       <c r="Y91" s="9" t="n"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>7.1.4</t>
-        </is>
-      </c>
-      <c r="B92" s="30" t="n"/>
-      <c r="C92" s="35" t="n"/>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>결과 정리 및 최종 보고</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>결과 분석 및 개선안 도출</t>
+        </is>
+      </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>비교 분석: 훈련 전후 KPI 변화, 통계적 유의성 검정, ROI 분석</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>KPI 변화 비교 분석 보고서</t>
+          <t>데이터 분석: Pandas/NumPy 기반 통계 분석, 회차별 KPI 비교, 개선율 산출</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>훈련 데이터 통계 분석 보고서</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
@@ -5208,39 +5188,35 @@
       <c r="T92" s="9" t="n"/>
       <c r="U92" s="9" t="n"/>
       <c r="V92" s="9" t="n"/>
-      <c r="W92" s="9" t="n"/>
-      <c r="X92" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="W92" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="X92" s="9" t="n"/>
       <c r="Y92" s="9" t="n"/>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>7.2.1</t>
+          <t>7.1.2</t>
         </is>
       </c>
       <c r="B93" s="30" t="n"/>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t>최종 산출물 작성</t>
-        </is>
-      </c>
+      <c r="C93" s="30" t="n"/>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>PoC 결과보고서: 프로젝트 개요, 기술 구현 내용, 성능 검증 결과, 향후 계획</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>PoC 최종 결과보고서</t>
+          <t>위험구간 분석: 병목 발생 Top 5 구간, 시간대별 패턴, 물리적 개선 권고사항</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>위험구간 분석</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="G93" s="10" t="n"/>
@@ -5263,30 +5239,30 @@
       <c r="T93" s="9" t="n"/>
       <c r="U93" s="9" t="n"/>
       <c r="V93" s="9" t="n"/>
-      <c r="W93" s="9" t="n"/>
-      <c r="X93" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="W93" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="X93" s="9" t="n"/>
       <c r="Y93" s="9" t="n"/>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>7.2.2</t>
+          <t>7.1.3</t>
         </is>
       </c>
       <c r="B94" s="30" t="n"/>
       <c r="C94" s="30" t="n"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>KPI 기준서: 최종 KPI 정의, 측정 방법론, 목표치 및 달성 결과</t>
-        </is>
-      </c>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t>KPI 평가 기준 및 달성 결과서</t>
+          <t>개선 방향: 모델 고도화 로드맵, 인프라 확장 계획, 운영 프로세스 개선안</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>기술 고도화 로드맵</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
@@ -5315,34 +5291,34 @@
       <c r="U94" s="9" t="n"/>
       <c r="V94" s="9" t="n"/>
       <c r="W94" s="9" t="n"/>
-      <c r="X94" s="9" t="n"/>
-      <c r="Y94" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="X94" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Y94" s="9" t="n"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>7.2.3</t>
+          <t>7.1.4</t>
         </is>
       </c>
       <c r="B95" s="30" t="n"/>
-      <c r="C95" s="30" t="n"/>
-      <c r="D95" s="11" t="inlineStr">
-        <is>
-          <t>데이터 구조 문서: API 스펙(OpenAPI 3.0), 데이터 플로우 다이어그램</t>
+      <c r="C95" s="35" t="n"/>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>비교 분석: 훈련 전후 KPI 변화, 통계적 유의성 검정, ROI 분석</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>ERD, API 스펙, 데이터 플로우 문서</t>
+          <t>KPI 변화 비교 분석 보고서</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="G95" s="10" t="n"/>
@@ -5366,29 +5342,33 @@
       <c r="U95" s="9" t="n"/>
       <c r="V95" s="9" t="n"/>
       <c r="W95" s="9" t="n"/>
-      <c r="X95" s="9" t="n"/>
-      <c r="Y95" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="X95" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Y95" s="9" t="n"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>7.2.4</t>
-        </is>
-      </c>
-      <c r="B96" s="35" t="n"/>
-      <c r="C96" s="35" t="n"/>
+          <t>7.2.1</t>
+        </is>
+      </c>
+      <c r="B96" s="30" t="n"/>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>최종 산출물 작성</t>
+        </is>
+      </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>운영 가이드: 시스템 운영 매뉴얼, 장애 대응 절차, 확장 가이드라인</t>
+          <t>PoC 결과보고서: 프로젝트 개요, 기술 구현 내용, 성능 검증 결과, 향후 계획</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>시스템 운영 매뉴얼 및 확장 가이드</t>
+          <t>PoC 최종 결과보고서</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
@@ -5417,8 +5397,161 @@
       <c r="U96" s="9" t="n"/>
       <c r="V96" s="9" t="n"/>
       <c r="W96" s="9" t="n"/>
-      <c r="X96" s="9" t="n"/>
-      <c r="Y96" s="9" t="inlineStr">
+      <c r="X96" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Y96" s="9" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>7.2.2</t>
+        </is>
+      </c>
+      <c r="B97" s="30" t="n"/>
+      <c r="C97" s="30" t="n"/>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>KPI 기준서: 최종 KPI 정의, 측정 방법론, 목표치 및 달성 결과</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>KPI 평가 기준 및 달성 결과서</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="n"/>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I97" s="8" t="n"/>
+      <c r="J97" s="9" t="n"/>
+      <c r="K97" s="9" t="n"/>
+      <c r="L97" s="9" t="n"/>
+      <c r="M97" s="9" t="n"/>
+      <c r="N97" s="9" t="n"/>
+      <c r="O97" s="9" t="n"/>
+      <c r="P97" s="9" t="n"/>
+      <c r="Q97" s="9" t="n"/>
+      <c r="R97" s="9" t="n"/>
+      <c r="S97" s="9" t="n"/>
+      <c r="T97" s="9" t="n"/>
+      <c r="U97" s="9" t="n"/>
+      <c r="V97" s="9" t="n"/>
+      <c r="W97" s="9" t="n"/>
+      <c r="X97" s="9" t="n"/>
+      <c r="Y97" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>7.2.3</t>
+        </is>
+      </c>
+      <c r="B98" s="30" t="n"/>
+      <c r="C98" s="30" t="n"/>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>데이터 구조 문서: API 스펙(OpenAPI 3.0), 데이터 플로우 다이어그램</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>ERD, API 스펙, 데이터 플로우 문서</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="n"/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I98" s="8" t="n"/>
+      <c r="J98" s="9" t="n"/>
+      <c r="K98" s="9" t="n"/>
+      <c r="L98" s="9" t="n"/>
+      <c r="M98" s="9" t="n"/>
+      <c r="N98" s="9" t="n"/>
+      <c r="O98" s="9" t="n"/>
+      <c r="P98" s="9" t="n"/>
+      <c r="Q98" s="9" t="n"/>
+      <c r="R98" s="9" t="n"/>
+      <c r="S98" s="9" t="n"/>
+      <c r="T98" s="9" t="n"/>
+      <c r="U98" s="9" t="n"/>
+      <c r="V98" s="9" t="n"/>
+      <c r="W98" s="9" t="n"/>
+      <c r="X98" s="9" t="n"/>
+      <c r="Y98" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>7.2.4</t>
+        </is>
+      </c>
+      <c r="B99" s="35" t="n"/>
+      <c r="C99" s="35" t="n"/>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>운영 가이드: 시스템 운영 매뉴얼, 장애 대응 절차, 확장 가이드라인</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>시스템 운영 매뉴얼 및 확장 가이드</t>
+        </is>
+      </c>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="n"/>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I99" s="8" t="n"/>
+      <c r="J99" s="9" t="n"/>
+      <c r="K99" s="9" t="n"/>
+      <c r="L99" s="9" t="n"/>
+      <c r="M99" s="9" t="n"/>
+      <c r="N99" s="9" t="n"/>
+      <c r="O99" s="9" t="n"/>
+      <c r="P99" s="9" t="n"/>
+      <c r="Q99" s="9" t="n"/>
+      <c r="R99" s="9" t="n"/>
+      <c r="S99" s="9" t="n"/>
+      <c r="T99" s="9" t="n"/>
+      <c r="U99" s="9" t="n"/>
+      <c r="V99" s="9" t="n"/>
+      <c r="W99" s="9" t="n"/>
+      <c r="X99" s="9" t="n"/>
+      <c r="Y99" s="9" t="inlineStr">
         <is>
           <t>V</t>
         </is>
@@ -5426,48 +5559,48 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="C43:C47"/>
-    <mergeCell ref="C73:C76"/>
-    <mergeCell ref="B38:B68"/>
-    <mergeCell ref="C89:C92"/>
+    <mergeCell ref="C49:C56"/>
+    <mergeCell ref="B80:B91"/>
     <mergeCell ref="B29:B37"/>
-    <mergeCell ref="C85:C88"/>
-    <mergeCell ref="C93:C96"/>
+    <mergeCell ref="C92:C95"/>
+    <mergeCell ref="C67:C71"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="C88:C91"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="D9:D11"/>
     <mergeCell ref="F9:F11"/>
+    <mergeCell ref="C84:C87"/>
+    <mergeCell ref="C57:C61"/>
     <mergeCell ref="G9:G11"/>
     <mergeCell ref="C25:C28"/>
+    <mergeCell ref="B72:B79"/>
     <mergeCell ref="B21:B28"/>
-    <mergeCell ref="C38:C42"/>
     <mergeCell ref="C12:C15"/>
     <mergeCell ref="C21:C24"/>
     <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C80:C83"/>
+    <mergeCell ref="R10:U10"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="R10:U10"/>
-    <mergeCell ref="B77:B88"/>
+    <mergeCell ref="C62:C66"/>
     <mergeCell ref="J10:M10"/>
+    <mergeCell ref="C76:C79"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="J9:Y9"/>
     <mergeCell ref="V10:Y10"/>
-    <mergeCell ref="C81:C84"/>
+    <mergeCell ref="C72:C75"/>
     <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C54:C58"/>
     <mergeCell ref="H9:H11"/>
-    <mergeCell ref="C64:C68"/>
-    <mergeCell ref="B69:B76"/>
+    <mergeCell ref="C44:C48"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="C29:C33"/>
-    <mergeCell ref="C69:C72"/>
+    <mergeCell ref="B92:B99"/>
     <mergeCell ref="B12:B20"/>
+    <mergeCell ref="C96:C99"/>
     <mergeCell ref="C34:C37"/>
     <mergeCell ref="C4:E4"/>
+    <mergeCell ref="B38:B71"/>
+    <mergeCell ref="C38:C43"/>
     <mergeCell ref="C16:C20"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C77:C80"/>
-    <mergeCell ref="C48:C53"/>
-    <mergeCell ref="C59:C63"/>
-    <mergeCell ref="B89:B96"/>
     <mergeCell ref="N10:Q10"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="E9:E11"/>

--- a/docs/weekly/2026-06-3주차/C-lab_PoC_WBS_v5.xlsx
+++ b/docs/weekly/2026-06-3주차/C-lab_PoC_WBS_v5.xlsx
@@ -265,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -363,6 +363,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -624,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:Y99"/>
+  <dimension ref="A1:Y103"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -639,6 +642,7 @@
     <col width="5" customWidth="1" min="10" max="25"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="17.25" customHeight="1">
       <c r="B2" s="29" t="inlineStr">
         <is>
@@ -703,7 +707,7 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>v5 (2026-06-17 갱신: 06-3주차 점검 — 완료 6건 + 누락 3항목 추가)</t>
+          <t>v5 (2026-06-17 갱신: 06-3주차 점검 — 완료 6 + 누락 3 + 스케일업 4.7 추가)</t>
         </is>
       </c>
       <c r="D5" s="24" t="n"/>
@@ -729,6 +733,7 @@
       <c r="D7" s="24" t="n"/>
       <c r="E7" s="25" t="n"/>
     </row>
+    <row r="8"/>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="32" t="inlineStr">
         <is>
@@ -4028,7 +4033,7 @@
           <t>4.6.5</t>
         </is>
       </c>
-      <c r="B71" s="35" t="n"/>
+      <c r="B71" s="30" t="n"/>
       <c r="C71" s="35" t="n"/>
       <c r="D71" s="13" t="inlineStr">
         <is>
@@ -4074,52 +4079,44 @@
       <c r="Y71" s="9" t="n"/>
     </row>
     <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>5.1.1</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>대시보드 및 리포트 개발</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>실시간 관제 화면 개발</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>인원 현황 시각화: D3.js/ECharts 기반 실시간 차트, WebGL 렌더링, 1초 갱신 주기</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>실시간 인원 현황 대시보드 (D3.js)</t>
-        </is>
-      </c>
-      <c r="F72" s="10" t="inlineStr">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>4.7.1</t>
+        </is>
+      </c>
+      <c r="B72" s="30" t="n"/>
+      <c r="C72" s="35" t="inlineStr">
+        <is>
+          <t>다채널 스케일업</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>1채널 통합 파이프라인 검증: 5대 분석 기능을 단일 스트림 실시간 파이프라인으로 통합·E2E 검증</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>1채널 통합 동작 검증 결과</t>
+        </is>
+      </c>
+      <c r="F72" s="15" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="G72" s="10" t="n"/>
-      <c r="H72" s="36" t="inlineStr">
+      <c r="G72" s="15" t="n"/>
+      <c r="H72" s="39" t="inlineStr">
         <is>
           <t>진행중</t>
         </is>
       </c>
-      <c r="I72" s="8" t="n"/>
+      <c r="I72" s="9" t="n"/>
       <c r="J72" s="9" t="n"/>
       <c r="K72" s="9" t="n"/>
       <c r="L72" s="9" t="n"/>
       <c r="M72" s="9" t="n"/>
-      <c r="N72" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="N72" s="9" t="n"/>
       <c r="O72" s="9" t="n"/>
       <c r="P72" s="9" t="n"/>
       <c r="Q72" s="9" t="n"/>
@@ -4133,44 +4130,40 @@
       <c r="Y72" s="9" t="n"/>
     </row>
     <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>5.1.2</t>
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>4.7.2</t>
         </is>
       </c>
       <c r="B73" s="30" t="n"/>
       <c r="C73" s="30" t="n"/>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>혼잡도 표시: 층별 평면도 오버레이, 색상 그라데이션(Green→Yellow→Red), 애니메이션 전환</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>층별 혼잡도 시각화 화면</t>
-        </is>
-      </c>
-      <c r="F73" s="10" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
-      <c r="G73" s="10" t="n"/>
-      <c r="H73" s="36" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="I73" s="8" t="n"/>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>15채널 동시 처리 확장: 동시 다잡 처리(직렬 락 해제), 채널별 트래커 인스턴스 분리, GPU 분산, 배치 추론, 채널 격리·큐 스케줄링</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>15채널 동시 처리 파이프라인</t>
+        </is>
+      </c>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>2w</t>
+        </is>
+      </c>
+      <c r="G73" s="15" t="n"/>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I73" s="9" t="n"/>
       <c r="J73" s="9" t="n"/>
       <c r="K73" s="9" t="n"/>
       <c r="L73" s="9" t="n"/>
       <c r="M73" s="9" t="n"/>
-      <c r="N73" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="N73" s="9" t="n"/>
       <c r="O73" s="9" t="n"/>
       <c r="P73" s="9" t="n"/>
       <c r="Q73" s="9" t="n"/>
@@ -4184,44 +4177,40 @@
       <c r="Y73" s="9" t="n"/>
     </row>
     <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>5.1.3</t>
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>4.7.3</t>
         </is>
       </c>
       <c r="B74" s="30" t="n"/>
       <c r="C74" s="30" t="n"/>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>경보 화면: Toast 알림, 사운드 경고, 이벤트 타임라인, 영상 팝업 재생</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>이벤트 경보 및 알림 UI</t>
-        </is>
-      </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
-      <c r="G74" s="10" t="n"/>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>150채널 스케일 달성: 대규모 동시 처리, VRAM/CPU 자원 최적화, 추적 경량화, GPU 증설 전제 검토</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>150채널 스케일 처리(목표 fps)</t>
+        </is>
+      </c>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>3w</t>
+        </is>
+      </c>
+      <c r="G74" s="15" t="n"/>
       <c r="H74" s="9" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I74" s="8" t="n"/>
+      <c r="I74" s="9" t="n"/>
       <c r="J74" s="9" t="n"/>
       <c r="K74" s="9" t="n"/>
       <c r="L74" s="9" t="n"/>
       <c r="M74" s="9" t="n"/>
-      <c r="N74" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="N74" s="9" t="n"/>
       <c r="O74" s="9" t="n"/>
       <c r="P74" s="9" t="n"/>
       <c r="Q74" s="9" t="n"/>
@@ -4235,44 +4224,40 @@
       <c r="Y74" s="9" t="n"/>
     </row>
     <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>5.1.4</t>
-        </is>
-      </c>
-      <c r="B75" s="30" t="n"/>
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>4.7.4</t>
+        </is>
+      </c>
+      <c r="B75" s="35" t="n"/>
       <c r="C75" s="35" t="n"/>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>관리자 UI: 사용자 관리, 카메라 설정, 임계값 조정, 시스템 로그 조회</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>관리자 설정 및 시스템 관리 UI</t>
-        </is>
-      </c>
-      <c r="F75" s="10" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
-      <c r="G75" s="10" t="n"/>
+      <c r="D75" s="13" t="inlineStr">
+        <is>
+          <t>스케일 성능 검증: 채널당 fps·총 throughput·VRAM·지연·연속운영 안정성 측정 및 회귀</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>다채널 스케일 성능 검증 보고</t>
+        </is>
+      </c>
+      <c r="F75" s="15" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="G75" s="15" t="n"/>
       <c r="H75" s="9" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I75" s="8" t="n"/>
+      <c r="I75" s="9" t="n"/>
       <c r="J75" s="9" t="n"/>
       <c r="K75" s="9" t="n"/>
       <c r="L75" s="9" t="n"/>
       <c r="M75" s="9" t="n"/>
-      <c r="N75" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="N75" s="9" t="n"/>
       <c r="O75" s="9" t="n"/>
       <c r="P75" s="9" t="n"/>
       <c r="Q75" s="9" t="n"/>
@@ -4288,23 +4273,27 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>5.2.1</t>
-        </is>
-      </c>
-      <c r="B76" s="30" t="n"/>
+          <t>5.1.1</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>대시보드 및 리포트 개발</t>
+        </is>
+      </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>분석 리포트 기능 개발</t>
+          <t>실시간 관제 화면 개발</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>KPI 산출: Apache Spark 배치 처리, 일/주/월 집계, 자동 리포트 생성(PDF/Excel)</t>
+          <t>인원 현황 시각화: D3.js/ECharts 기반 실시간 차트, WebGL 렌더링, 1초 갱신 주기</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>KPI 자동 산출 배치 모듈 (Spark)</t>
+          <t>실시간 인원 현황 대시보드 (D3.js)</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -4313,9 +4302,9 @@
         </is>
       </c>
       <c r="G76" s="10" t="n"/>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="H76" s="36" t="inlineStr">
+        <is>
+          <t>진행중</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
@@ -4323,12 +4312,12 @@
       <c r="K76" s="9" t="n"/>
       <c r="L76" s="9" t="n"/>
       <c r="M76" s="9" t="n"/>
-      <c r="N76" s="9" t="n"/>
-      <c r="O76" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="N76" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="O76" s="9" t="n"/>
       <c r="P76" s="9" t="n"/>
       <c r="Q76" s="9" t="n"/>
       <c r="R76" s="9" t="n"/>
@@ -4343,19 +4332,19 @@
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>5.2.2</t>
+          <t>5.1.2</t>
         </is>
       </c>
       <c r="B77" s="30" t="n"/>
       <c r="C77" s="30" t="n"/>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>히트맵 시각화: Heatmap.js, 시간별 밀집 패턴, 동선 궤적 오버레이, 재생 기능</t>
+          <t>혼잡도 표시: 층별 평면도 오버레이, 색상 그라데이션(Green→Yellow→Red), 애니메이션 전환</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>동선 히트맵 시각화 모듈</t>
+          <t>층별 혼잡도 시각화 화면</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
@@ -4364,9 +4353,9 @@
         </is>
       </c>
       <c r="G77" s="10" t="n"/>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="H77" s="36" t="inlineStr">
+        <is>
+          <t>진행중</t>
         </is>
       </c>
       <c r="I77" s="8" t="n"/>
@@ -4374,12 +4363,12 @@
       <c r="K77" s="9" t="n"/>
       <c r="L77" s="9" t="n"/>
       <c r="M77" s="9" t="n"/>
-      <c r="N77" s="9" t="n"/>
-      <c r="O77" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="N77" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="O77" s="9" t="n"/>
       <c r="P77" s="9" t="n"/>
       <c r="Q77" s="9" t="n"/>
       <c r="R77" s="9" t="n"/>
@@ -4394,19 +4383,19 @@
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>5.2.3</t>
+          <t>5.1.3</t>
         </is>
       </c>
       <c r="B78" s="30" t="n"/>
       <c r="C78" s="30" t="n"/>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>비교 리포트: 회차별 KPI 테이블, 개선율 그래프, 통계적 유의성 검정(t-test)</t>
+          <t>경보 화면: Toast 알림, 사운드 경고, 이벤트 타임라인, 영상 팝업 재생</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>회차별 비교 리포트 생성기</t>
+          <t>이벤트 경보 및 알림 UI</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
@@ -4425,12 +4414,12 @@
       <c r="K78" s="9" t="n"/>
       <c r="L78" s="9" t="n"/>
       <c r="M78" s="9" t="n"/>
-      <c r="N78" s="9" t="n"/>
-      <c r="O78" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="N78" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="O78" s="9" t="n"/>
       <c r="P78" s="9" t="n"/>
       <c r="Q78" s="9" t="n"/>
       <c r="R78" s="9" t="n"/>
@@ -4445,19 +4434,19 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>5.2.4</t>
-        </is>
-      </c>
-      <c r="B79" s="35" t="n"/>
+          <t>5.1.4</t>
+        </is>
+      </c>
+      <c r="B79" s="30" t="n"/>
       <c r="C79" s="35" t="n"/>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>로그 저장: Elasticsearch 인덱싱, Kibana 대시보드, 90일 보존 정책, 압축 아카이빙</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이벤트 로그 저장 및 검색 시스템 </t>
+          <t>관리자 UI: 사용자 관리, 카메라 설정, 임계값 조정, 시스템 로그 조회</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>관리자 설정 및 시스템 관리 UI</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
@@ -4476,12 +4465,12 @@
       <c r="K79" s="9" t="n"/>
       <c r="L79" s="9" t="n"/>
       <c r="M79" s="9" t="n"/>
-      <c r="N79" s="9" t="n"/>
-      <c r="O79" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="N79" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="O79" s="9" t="n"/>
       <c r="P79" s="9" t="n"/>
       <c r="Q79" s="9" t="n"/>
       <c r="R79" s="9" t="n"/>
@@ -4496,32 +4485,28 @@
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>6.1.1</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>현장 실증 및 성능 검증</t>
-        </is>
-      </c>
+          <t>5.2.1</t>
+        </is>
+      </c>
+      <c r="B80" s="30" t="n"/>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>현장 실증 수행</t>
-        </is>
-      </c>
-      <c r="D80" s="11" t="inlineStr">
-        <is>
-          <t>현장 테스트: 피난훈련  수행, 50/100/200인 규모 파악</t>
-        </is>
-      </c>
-      <c r="E80" s="11" t="inlineStr">
-        <is>
-          <t>현장 테스트</t>
+          <t>분석 리포트 기능 개발</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>KPI 산출: Apache Spark 배치 처리, 일/주/월 집계, 자동 리포트 생성(PDF/Excel)</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>KPI 자동 산출 배치 모듈 (Spark)</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>1w</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="G80" s="10" t="n"/>
@@ -4536,14 +4521,14 @@
       <c r="L80" s="9" t="n"/>
       <c r="M80" s="9" t="n"/>
       <c r="N80" s="9" t="n"/>
-      <c r="O80" s="9" t="n"/>
+      <c r="O80" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="P80" s="9" t="n"/>
       <c r="Q80" s="9" t="n"/>
-      <c r="R80" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="R80" s="9" t="n"/>
       <c r="S80" s="9" t="n"/>
       <c r="T80" s="9" t="n"/>
       <c r="U80" s="9" t="n"/>
@@ -4555,24 +4540,24 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>5.2.2</t>
         </is>
       </c>
       <c r="B81" s="30" t="n"/>
       <c r="C81" s="30" t="n"/>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>시나리오별 검증: 정상 대피, 병목 발생, 역류 상황, 복합 이상상황 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="E81" s="11" t="inlineStr">
-        <is>
-          <t>시나리오별 기능 검증</t>
+          <t>히트맵 시각화: Heatmap.js, 시간별 밀집 패턴, 동선 궤적 오버레이, 재생 기능</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>동선 히트맵 시각화 모듈</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>1w</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="G81" s="10" t="n"/>
@@ -4587,15 +4572,15 @@
       <c r="L81" s="9" t="n"/>
       <c r="M81" s="9" t="n"/>
       <c r="N81" s="9" t="n"/>
-      <c r="O81" s="9" t="n"/>
+      <c r="O81" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="P81" s="9" t="n"/>
       <c r="Q81" s="9" t="n"/>
       <c r="R81" s="9" t="n"/>
-      <c r="S81" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="S81" s="9" t="n"/>
       <c r="T81" s="9" t="n"/>
       <c r="U81" s="9" t="n"/>
       <c r="V81" s="9" t="n"/>
@@ -4606,24 +4591,24 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>6.1.3</t>
+          <t>5.2.3</t>
         </is>
       </c>
       <c r="B82" s="30" t="n"/>
       <c r="C82" s="30" t="n"/>
-      <c r="D82" s="11" t="inlineStr">
-        <is>
-          <t>피드백 수집: 운영자 인터뷰,  UI/UX 개선사항 도출</t>
-        </is>
-      </c>
-      <c r="E82" s="11" t="inlineStr">
-        <is>
-          <t>운영자 피드백</t>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>비교 리포트: 회차별 KPI 테이블, 개선율 그래프, 통계적 유의성 검정(t-test)</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>회차별 비교 리포트 생성기</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>1w</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="G82" s="10" t="n"/>
@@ -4638,16 +4623,16 @@
       <c r="L82" s="9" t="n"/>
       <c r="M82" s="9" t="n"/>
       <c r="N82" s="9" t="n"/>
-      <c r="O82" s="9" t="n"/>
+      <c r="O82" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="P82" s="9" t="n"/>
       <c r="Q82" s="9" t="n"/>
       <c r="R82" s="9" t="n"/>
       <c r="S82" s="9" t="n"/>
-      <c r="T82" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="T82" s="9" t="n"/>
       <c r="U82" s="9" t="n"/>
       <c r="V82" s="9" t="n"/>
       <c r="W82" s="9" t="n"/>
@@ -4657,24 +4642,24 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>6.1.4</t>
-        </is>
-      </c>
-      <c r="B83" s="30" t="n"/>
+          <t>5.2.4</t>
+        </is>
+      </c>
+      <c r="B83" s="35" t="n"/>
       <c r="C83" s="35" t="n"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>병목구간 분석: 이벤트 로그 기반 병목 빈도, 위치, 지속시간 분석, 개선 우선순위 도출</t>
+          <t>로그 저장: Elasticsearch 인덱싱, Kibana 대시보드, 90일 보존 정책, 압축 아카이빙</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>병목구간 분석</t>
+          <t xml:space="preserve">이벤트 로그 저장 및 검색 시스템 </t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>1w</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="G83" s="10" t="n"/>
@@ -4689,17 +4674,17 @@
       <c r="L83" s="9" t="n"/>
       <c r="M83" s="9" t="n"/>
       <c r="N83" s="9" t="n"/>
-      <c r="O83" s="9" t="n"/>
+      <c r="O83" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="P83" s="9" t="n"/>
       <c r="Q83" s="9" t="n"/>
       <c r="R83" s="9" t="n"/>
       <c r="S83" s="9" t="n"/>
       <c r="T83" s="9" t="n"/>
-      <c r="U83" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="U83" s="9" t="n"/>
       <c r="V83" s="9" t="n"/>
       <c r="W83" s="9" t="n"/>
       <c r="X83" s="9" t="n"/>
@@ -4708,28 +4693,32 @@
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>6.2.1</t>
-        </is>
-      </c>
-      <c r="B84" s="30" t="n"/>
+          <t>6.1.1</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>현장 실증 및 성능 검증</t>
+        </is>
+      </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>성능 검증 및 최적화</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>탐지 정확도 검증: Precision/Recall/F1-score 측정, Confusion Matrix, 오탐/미탐 사례 분석</t>
+          <t>현장 실증 수행</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>현장 테스트: 피난훈련  수행, 50/100/200인 규모 파악</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>탐지 정확도 검증</t>
+          <t>현장 테스트</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>2w</t>
+          <t>1w</t>
         </is>
       </c>
       <c r="G84" s="10" t="n"/>
@@ -4745,17 +4734,13 @@
       <c r="M84" s="9" t="n"/>
       <c r="N84" s="9" t="n"/>
       <c r="O84" s="9" t="n"/>
-      <c r="P84" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="Q84" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="R84" s="9" t="n"/>
+      <c r="P84" s="9" t="n"/>
+      <c r="Q84" s="9" t="n"/>
+      <c r="R84" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="S84" s="9" t="n"/>
       <c r="T84" s="9" t="n"/>
       <c r="U84" s="9" t="n"/>
@@ -4767,24 +4752,24 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>6.2.2</t>
+          <t>6.1.2</t>
         </is>
       </c>
       <c r="B85" s="30" t="n"/>
       <c r="C85" s="30" t="n"/>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>이벤트 탐지 검증: 이벤트별 탐지율, 평균 탐지 지연시간, False Positive Rate 측정</t>
+          <t>시나리오별 검증: 정상 대피, 병목 발생, 역류 상황, 복합 이상상황 시뮬레이션</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>이벤트 탐지 성능 검증</t>
+          <t>시나리오별 기능 검증</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>2w</t>
+          <t>1w</t>
         </is>
       </c>
       <c r="G85" s="10" t="n"/>
@@ -4800,18 +4785,14 @@
       <c r="M85" s="9" t="n"/>
       <c r="N85" s="9" t="n"/>
       <c r="O85" s="9" t="n"/>
-      <c r="P85" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="Q85" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="P85" s="9" t="n"/>
+      <c r="Q85" s="9" t="n"/>
       <c r="R85" s="9" t="n"/>
-      <c r="S85" s="9" t="n"/>
+      <c r="S85" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="T85" s="9" t="n"/>
       <c r="U85" s="9" t="n"/>
       <c r="V85" s="9" t="n"/>
@@ -4822,24 +4803,24 @@
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>6.2.3</t>
+          <t>6.1.3</t>
         </is>
       </c>
       <c r="B86" s="30" t="n"/>
       <c r="C86" s="30" t="n"/>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>오탐/미탐 분석: 오탐 원인(조명, 반사, 그림자), 미탐 원인(가림, 밀집), 개선 방안 도출</t>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>피드백 수집: 운영자 인터뷰,  UI/UX 개선사항 도출</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>오탐/미탐 원인 분석</t>
+          <t>운영자 피드백</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>2w</t>
+          <t>1w</t>
         </is>
       </c>
       <c r="G86" s="10" t="n"/>
@@ -4855,19 +4836,15 @@
       <c r="M86" s="9" t="n"/>
       <c r="N86" s="9" t="n"/>
       <c r="O86" s="9" t="n"/>
-      <c r="P86" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="Q86" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="P86" s="9" t="n"/>
+      <c r="Q86" s="9" t="n"/>
       <c r="R86" s="9" t="n"/>
       <c r="S86" s="9" t="n"/>
-      <c r="T86" s="9" t="n"/>
+      <c r="T86" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="U86" s="9" t="n"/>
       <c r="V86" s="9" t="n"/>
       <c r="W86" s="9" t="n"/>
@@ -4877,24 +4854,24 @@
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>6.2.4</t>
+          <t>6.1.4</t>
         </is>
       </c>
       <c r="B87" s="30" t="n"/>
       <c r="C87" s="35" t="n"/>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>서버 안정성: 24시간 연속 운영 테스트, CPU/GPU 사용률, 메모리 누수, OOM 발생 여부</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t>24시간 안정성 테스트</t>
+          <t>병목구간 분석: 이벤트 로그 기반 병목 빈도, 위치, 지속시간 분석, 개선 우선순위 도출</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>병목구간 분석</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>2w</t>
+          <t>1w</t>
         </is>
       </c>
       <c r="G87" s="10" t="n"/>
@@ -4910,20 +4887,16 @@
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="9" t="n"/>
       <c r="O87" s="9" t="n"/>
-      <c r="P87" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="Q87" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="P87" s="9" t="n"/>
+      <c r="Q87" s="9" t="n"/>
       <c r="R87" s="9" t="n"/>
       <c r="S87" s="9" t="n"/>
       <c r="T87" s="9" t="n"/>
-      <c r="U87" s="9" t="n"/>
+      <c r="U87" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="V87" s="9" t="n"/>
       <c r="W87" s="9" t="n"/>
       <c r="X87" s="9" t="n"/>
@@ -4932,28 +4905,28 @@
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>6.3.1</t>
+          <t>6.2.1</t>
         </is>
       </c>
       <c r="B88" s="30" t="n"/>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>기능 안정화 및 운영 최적화</t>
+          <t>성능 검증 및 최적화</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>기능 개선: 현장 이슈 기반 핫픽스, 모델 재학습, 임계값 재조정</t>
+          <t>탐지 정확도 검증: Precision/Recall/F1-score 측정, Confusion Matrix, 오탐/미탐 사례 분석</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">현장 이슈 기반 핫픽스 </t>
+          <t>탐지 정확도 검증</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>2w</t>
         </is>
       </c>
       <c r="G88" s="10" t="n"/>
@@ -4969,17 +4942,21 @@
       <c r="M88" s="9" t="n"/>
       <c r="N88" s="9" t="n"/>
       <c r="O88" s="9" t="n"/>
-      <c r="P88" s="9" t="n"/>
-      <c r="Q88" s="9" t="n"/>
+      <c r="P88" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Q88" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="R88" s="9" t="n"/>
       <c r="S88" s="9" t="n"/>
       <c r="T88" s="9" t="n"/>
       <c r="U88" s="9" t="n"/>
-      <c r="V88" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="V88" s="9" t="n"/>
       <c r="W88" s="9" t="n"/>
       <c r="X88" s="9" t="n"/>
       <c r="Y88" s="9" t="n"/>
@@ -4987,24 +4964,24 @@
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>6.3.2</t>
+          <t>6.2.2</t>
         </is>
       </c>
       <c r="B89" s="30" t="n"/>
       <c r="C89" s="30" t="n"/>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>성능 튜닝: TensorRT 최적화, Batch Size 조정, 멀티스레딩, 메모리 풀링</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>TensorRT 최적화 성능 개선</t>
+          <t>이벤트 탐지 검증: 이벤트별 탐지율, 평균 탐지 지연시간, False Positive Rate 측정</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>이벤트 탐지 성능 검증</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>2w</t>
         </is>
       </c>
       <c r="G89" s="10" t="n"/>
@@ -5020,17 +4997,21 @@
       <c r="M89" s="9" t="n"/>
       <c r="N89" s="9" t="n"/>
       <c r="O89" s="9" t="n"/>
-      <c r="P89" s="9" t="n"/>
-      <c r="Q89" s="9" t="n"/>
+      <c r="P89" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Q89" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="R89" s="9" t="n"/>
       <c r="S89" s="9" t="n"/>
       <c r="T89" s="9" t="n"/>
       <c r="U89" s="9" t="n"/>
-      <c r="V89" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="V89" s="9" t="n"/>
       <c r="W89" s="9" t="n"/>
       <c r="X89" s="9" t="n"/>
       <c r="Y89" s="9" t="n"/>
@@ -5038,24 +5019,24 @@
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>6.3.3</t>
+          <t>6.2.3</t>
         </is>
       </c>
       <c r="B90" s="30" t="n"/>
       <c r="C90" s="30" t="n"/>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>UI 보완: 사용자 피드백 반영, 반응형 레이아웃, 접근성(A11y) 개선</t>
-        </is>
-      </c>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t>UI/UX 개선 적용</t>
+          <t>오탐/미탐 분석: 오탐 원인(조명, 반사, 그림자), 미탐 원인(가림, 밀집), 개선 방안 도출</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>오탐/미탐 원인 분석</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>2w</t>
         </is>
       </c>
       <c r="G90" s="10" t="n"/>
@@ -5071,42 +5052,46 @@
       <c r="M90" s="9" t="n"/>
       <c r="N90" s="9" t="n"/>
       <c r="O90" s="9" t="n"/>
-      <c r="P90" s="9" t="n"/>
-      <c r="Q90" s="9" t="n"/>
+      <c r="P90" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Q90" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="R90" s="9" t="n"/>
       <c r="S90" s="9" t="n"/>
       <c r="T90" s="9" t="n"/>
       <c r="U90" s="9" t="n"/>
       <c r="V90" s="9" t="n"/>
-      <c r="W90" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="W90" s="9" t="n"/>
       <c r="X90" s="9" t="n"/>
       <c r="Y90" s="9" t="n"/>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>6.3.4</t>
-        </is>
-      </c>
-      <c r="B91" s="35" t="n"/>
+          <t>6.2.4</t>
+        </is>
+      </c>
+      <c r="B91" s="30" t="n"/>
       <c r="C91" s="35" t="n"/>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>통합 테스트: End-to-End 시나리오, 부하 테스트(Locust), 장애 복구(Failover) 검증</t>
+          <t>서버 안정성: 24시간 연속 운영 테스트, CPU/GPU 사용률, 메모리 누수, OOM 발생 여부</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>E2E 통합 테스트 및 부하 테스트</t>
+          <t>24시간 안정성 테스트</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>2w</t>
         </is>
       </c>
       <c r="G91" s="10" t="n"/>
@@ -5122,45 +5107,45 @@
       <c r="M91" s="9" t="n"/>
       <c r="N91" s="9" t="n"/>
       <c r="O91" s="9" t="n"/>
-      <c r="P91" s="9" t="n"/>
-      <c r="Q91" s="9" t="n"/>
+      <c r="P91" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Q91" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="R91" s="9" t="n"/>
       <c r="S91" s="9" t="n"/>
       <c r="T91" s="9" t="n"/>
       <c r="U91" s="9" t="n"/>
       <c r="V91" s="9" t="n"/>
-      <c r="W91" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="W91" s="9" t="n"/>
       <c r="X91" s="9" t="n"/>
       <c r="Y91" s="9" t="n"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>7.1.1</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>결과 정리 및 최종 보고</t>
-        </is>
-      </c>
+          <t>6.3.1</t>
+        </is>
+      </c>
+      <c r="B92" s="30" t="n"/>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>결과 분석 및 개선안 도출</t>
+          <t>기능 안정화 및 운영 최적화</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>데이터 분석: Pandas/NumPy 기반 통계 분석, 회차별 KPI 비교, 개선율 산출</t>
+          <t>기능 개선: 현장 이슈 기반 핫픽스, 모델 재학습, 임계값 재조정</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>훈련 데이터 통계 분석 보고서</t>
+          <t xml:space="preserve">현장 이슈 기반 핫픽스 </t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
@@ -5187,31 +5172,31 @@
       <c r="S92" s="9" t="n"/>
       <c r="T92" s="9" t="n"/>
       <c r="U92" s="9" t="n"/>
-      <c r="V92" s="9" t="n"/>
-      <c r="W92" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="V92" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W92" s="9" t="n"/>
       <c r="X92" s="9" t="n"/>
       <c r="Y92" s="9" t="n"/>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>7.1.2</t>
+          <t>6.3.2</t>
         </is>
       </c>
       <c r="B93" s="30" t="n"/>
       <c r="C93" s="30" t="n"/>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>위험구간 분석: 병목 발생 Top 5 구간, 시간대별 패턴, 물리적 개선 권고사항</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="inlineStr">
-        <is>
-          <t>위험구간 분석</t>
+          <t>성능 튜닝: TensorRT 최적화, Batch Size 조정, 멀티스레딩, 메모리 풀링</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>TensorRT 최적화 성능 개선</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
@@ -5238,36 +5223,36 @@
       <c r="S93" s="9" t="n"/>
       <c r="T93" s="9" t="n"/>
       <c r="U93" s="9" t="n"/>
-      <c r="V93" s="9" t="n"/>
-      <c r="W93" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="V93" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W93" s="9" t="n"/>
       <c r="X93" s="9" t="n"/>
       <c r="Y93" s="9" t="n"/>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>7.1.3</t>
+          <t>6.3.3</t>
         </is>
       </c>
       <c r="B94" s="30" t="n"/>
       <c r="C94" s="30" t="n"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>개선 방향: 모델 고도화 로드맵, 인프라 확장 계획, 운영 프로세스 개선안</t>
-        </is>
-      </c>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>기술 고도화 로드맵</t>
+          <t>UI 보완: 사용자 피드백 반영, 반응형 레이아웃, 접근성(A11y) 개선</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>UI/UX 개선 적용</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="G94" s="10" t="n"/>
@@ -5290,30 +5275,30 @@
       <c r="T94" s="9" t="n"/>
       <c r="U94" s="9" t="n"/>
       <c r="V94" s="9" t="n"/>
-      <c r="W94" s="9" t="n"/>
-      <c r="X94" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="W94" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="X94" s="9" t="n"/>
       <c r="Y94" s="9" t="n"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>7.1.4</t>
-        </is>
-      </c>
-      <c r="B95" s="30" t="n"/>
+          <t>6.3.4</t>
+        </is>
+      </c>
+      <c r="B95" s="35" t="n"/>
       <c r="C95" s="35" t="n"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>비교 분석: 훈련 전후 KPI 변화, 통계적 유의성 검정, ROI 분석</t>
+          <t>통합 테스트: End-to-End 시나리오, 부하 테스트(Locust), 장애 복구(Failover) 검증</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>KPI 변화 비교 분석 보고서</t>
+          <t>E2E 통합 테스트 및 부하 테스트</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
@@ -5341,39 +5326,43 @@
       <c r="T95" s="9" t="n"/>
       <c r="U95" s="9" t="n"/>
       <c r="V95" s="9" t="n"/>
-      <c r="W95" s="9" t="n"/>
-      <c r="X95" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="W95" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="X95" s="9" t="n"/>
       <c r="Y95" s="9" t="n"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>7.2.1</t>
-        </is>
-      </c>
-      <c r="B96" s="30" t="n"/>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>결과 정리 및 최종 보고</t>
+        </is>
+      </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>최종 산출물 작성</t>
+          <t>결과 분석 및 개선안 도출</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>PoC 결과보고서: 프로젝트 개요, 기술 구현 내용, 성능 검증 결과, 향후 계획</t>
-        </is>
-      </c>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t>PoC 최종 결과보고서</t>
+          <t>데이터 분석: Pandas/NumPy 기반 통계 분석, 회차별 KPI 비교, 개선율 산출</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>훈련 데이터 통계 분석 보고서</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="G96" s="10" t="n"/>
@@ -5396,35 +5385,35 @@
       <c r="T96" s="9" t="n"/>
       <c r="U96" s="9" t="n"/>
       <c r="V96" s="9" t="n"/>
-      <c r="W96" s="9" t="n"/>
-      <c r="X96" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="W96" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="X96" s="9" t="n"/>
       <c r="Y96" s="9" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>7.2.2</t>
+          <t>7.1.2</t>
         </is>
       </c>
       <c r="B97" s="30" t="n"/>
       <c r="C97" s="30" t="n"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>KPI 기준서: 최종 KPI 정의, 측정 방법론, 목표치 및 달성 결과</t>
-        </is>
-      </c>
-      <c r="E97" s="8" t="inlineStr">
-        <is>
-          <t>KPI 평가 기준 및 달성 결과서</t>
+          <t>위험구간 분석: 병목 발생 Top 5 구간, 시간대별 패턴, 물리적 개선 권고사항</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>위험구간 분석</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="G97" s="10" t="n"/>
@@ -5447,30 +5436,30 @@
       <c r="T97" s="9" t="n"/>
       <c r="U97" s="9" t="n"/>
       <c r="V97" s="9" t="n"/>
-      <c r="W97" s="9" t="n"/>
+      <c r="W97" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="X97" s="9" t="n"/>
-      <c r="Y97" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="Y97" s="9" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>7.2.3</t>
+          <t>7.1.3</t>
         </is>
       </c>
       <c r="B98" s="30" t="n"/>
       <c r="C98" s="30" t="n"/>
-      <c r="D98" s="11" t="inlineStr">
-        <is>
-          <t>데이터 구조 문서: API 스펙(OpenAPI 3.0), 데이터 플로우 다이어그램</t>
-        </is>
-      </c>
-      <c r="E98" s="8" t="inlineStr">
-        <is>
-          <t>ERD, API 스펙, 데이터 플로우 문서</t>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>개선 방향: 모델 고도화 로드맵, 인프라 확장 계획, 운영 프로세스 개선안</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>기술 고도화 로드맵</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
@@ -5499,34 +5488,34 @@
       <c r="U98" s="9" t="n"/>
       <c r="V98" s="9" t="n"/>
       <c r="W98" s="9" t="n"/>
-      <c r="X98" s="9" t="n"/>
-      <c r="Y98" s="9" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="X98" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Y98" s="9" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>7.2.4</t>
-        </is>
-      </c>
-      <c r="B99" s="35" t="n"/>
+          <t>7.1.4</t>
+        </is>
+      </c>
+      <c r="B99" s="30" t="n"/>
       <c r="C99" s="35" t="n"/>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>운영 가이드: 시스템 운영 매뉴얼, 장애 대응 절차, 확장 가이드라인</t>
+          <t>비교 분석: 훈련 전후 KPI 변화, 통계적 유의성 검정, ROI 분석</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>시스템 운영 매뉴얼 및 확장 가이드</t>
+          <t>KPI 변화 비교 분석 보고서</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="G99" s="10" t="n"/>
@@ -5550,29 +5539,239 @@
       <c r="U99" s="9" t="n"/>
       <c r="V99" s="9" t="n"/>
       <c r="W99" s="9" t="n"/>
-      <c r="X99" s="9" t="n"/>
-      <c r="Y99" s="9" t="inlineStr">
+      <c r="X99" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Y99" s="9" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>7.2.1</t>
+        </is>
+      </c>
+      <c r="B100" s="30" t="n"/>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>최종 산출물 작성</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>PoC 결과보고서: 프로젝트 개요, 기술 구현 내용, 성능 검증 결과, 향후 계획</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>PoC 최종 결과보고서</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="n"/>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I100" s="8" t="n"/>
+      <c r="J100" s="9" t="n"/>
+      <c r="K100" s="9" t="n"/>
+      <c r="L100" s="9" t="n"/>
+      <c r="M100" s="9" t="n"/>
+      <c r="N100" s="9" t="n"/>
+      <c r="O100" s="9" t="n"/>
+      <c r="P100" s="9" t="n"/>
+      <c r="Q100" s="9" t="n"/>
+      <c r="R100" s="9" t="n"/>
+      <c r="S100" s="9" t="n"/>
+      <c r="T100" s="9" t="n"/>
+      <c r="U100" s="9" t="n"/>
+      <c r="V100" s="9" t="n"/>
+      <c r="W100" s="9" t="n"/>
+      <c r="X100" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="Y100" s="9" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>7.2.2</t>
+        </is>
+      </c>
+      <c r="B101" s="30" t="n"/>
+      <c r="C101" s="30" t="n"/>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>KPI 기준서: 최종 KPI 정의, 측정 방법론, 목표치 및 달성 결과</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>KPI 평가 기준 및 달성 결과서</t>
+        </is>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="G101" s="10" t="n"/>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I101" s="8" t="n"/>
+      <c r="J101" s="9" t="n"/>
+      <c r="K101" s="9" t="n"/>
+      <c r="L101" s="9" t="n"/>
+      <c r="M101" s="9" t="n"/>
+      <c r="N101" s="9" t="n"/>
+      <c r="O101" s="9" t="n"/>
+      <c r="P101" s="9" t="n"/>
+      <c r="Q101" s="9" t="n"/>
+      <c r="R101" s="9" t="n"/>
+      <c r="S101" s="9" t="n"/>
+      <c r="T101" s="9" t="n"/>
+      <c r="U101" s="9" t="n"/>
+      <c r="V101" s="9" t="n"/>
+      <c r="W101" s="9" t="n"/>
+      <c r="X101" s="9" t="n"/>
+      <c r="Y101" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>7.2.3</t>
+        </is>
+      </c>
+      <c r="B102" s="30" t="n"/>
+      <c r="C102" s="30" t="n"/>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>데이터 구조 문서: API 스펙(OpenAPI 3.0), 데이터 플로우 다이어그램</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>ERD, API 스펙, 데이터 플로우 문서</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="n"/>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I102" s="8" t="n"/>
+      <c r="J102" s="9" t="n"/>
+      <c r="K102" s="9" t="n"/>
+      <c r="L102" s="9" t="n"/>
+      <c r="M102" s="9" t="n"/>
+      <c r="N102" s="9" t="n"/>
+      <c r="O102" s="9" t="n"/>
+      <c r="P102" s="9" t="n"/>
+      <c r="Q102" s="9" t="n"/>
+      <c r="R102" s="9" t="n"/>
+      <c r="S102" s="9" t="n"/>
+      <c r="T102" s="9" t="n"/>
+      <c r="U102" s="9" t="n"/>
+      <c r="V102" s="9" t="n"/>
+      <c r="W102" s="9" t="n"/>
+      <c r="X102" s="9" t="n"/>
+      <c r="Y102" s="9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>7.2.4</t>
+        </is>
+      </c>
+      <c r="B103" s="35" t="n"/>
+      <c r="C103" s="35" t="n"/>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>운영 가이드: 시스템 운영 매뉴얼, 장애 대응 절차, 확장 가이드라인</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>시스템 운영 매뉴얼 및 확장 가이드</t>
+        </is>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="G103" s="10" t="n"/>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I103" s="8" t="n"/>
+      <c r="J103" s="9" t="n"/>
+      <c r="K103" s="9" t="n"/>
+      <c r="L103" s="9" t="n"/>
+      <c r="M103" s="9" t="n"/>
+      <c r="N103" s="9" t="n"/>
+      <c r="O103" s="9" t="n"/>
+      <c r="P103" s="9" t="n"/>
+      <c r="Q103" s="9" t="n"/>
+      <c r="R103" s="9" t="n"/>
+      <c r="S103" s="9" t="n"/>
+      <c r="T103" s="9" t="n"/>
+      <c r="U103" s="9" t="n"/>
+      <c r="V103" s="9" t="n"/>
+      <c r="W103" s="9" t="n"/>
+      <c r="X103" s="9" t="n"/>
+      <c r="Y103" s="9" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="46">
     <mergeCell ref="C49:C56"/>
-    <mergeCell ref="B80:B91"/>
+    <mergeCell ref="B38:B75"/>
+    <mergeCell ref="B76:B83"/>
     <mergeCell ref="B29:B37"/>
     <mergeCell ref="C92:C95"/>
     <mergeCell ref="C67:C71"/>
     <mergeCell ref="D9:D11"/>
+    <mergeCell ref="C2:E2"/>
     <mergeCell ref="C88:C91"/>
-    <mergeCell ref="C2:E2"/>
     <mergeCell ref="F9:F11"/>
+    <mergeCell ref="C57:C61"/>
     <mergeCell ref="C84:C87"/>
-    <mergeCell ref="C57:C61"/>
     <mergeCell ref="G9:G11"/>
+    <mergeCell ref="C100:C103"/>
+    <mergeCell ref="B96:B103"/>
     <mergeCell ref="C25:C28"/>
-    <mergeCell ref="B72:B79"/>
     <mergeCell ref="B21:B28"/>
     <mergeCell ref="C12:C15"/>
     <mergeCell ref="C21:C24"/>
@@ -5592,14 +5791,13 @@
     <mergeCell ref="C44:C48"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="C29:C33"/>
-    <mergeCell ref="B92:B99"/>
+    <mergeCell ref="B84:B95"/>
     <mergeCell ref="B12:B20"/>
     <mergeCell ref="C96:C99"/>
     <mergeCell ref="C34:C37"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="B38:B71"/>
+    <mergeCell ref="C16:C20"/>
     <mergeCell ref="C38:C43"/>
-    <mergeCell ref="C16:C20"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="N10:Q10"/>
     <mergeCell ref="C9:C11"/>
